--- a/output/xlsx/eoss-401.xlsx
+++ b/output/xlsx/eoss-401.xlsx
@@ -3816,7 +3816,7 @@
         <v>46151.29412787037</v>
       </c>
       <c r="D2" s="1">
-        <v>46151.54409722222</v>
+        <v>46151.29409722222</v>
       </c>
       <c r="E2">
         <v>5214</v>
@@ -3902,7 +3902,7 @@
         <v>46151.29429356482</v>
       </c>
       <c r="D3" s="1">
-        <v>46151.544270833336</v>
+        <v>46151.294270833336</v>
       </c>
       <c r="E3">
         <v>5346</v>
@@ -4033,7 +4033,7 @@
         <v>46151.29447340278</v>
       </c>
       <c r="D4" s="1">
-        <v>46151.544444444444</v>
+        <v>46151.294444444444</v>
       </c>
       <c r="E4">
         <v>5634</v>
@@ -4155,7 +4155,7 @@
         <v>46151.29464011574</v>
       </c>
       <c r="D5" s="1">
-        <v>46151.54461805556</v>
+        <v>46151.29461805556</v>
       </c>
       <c r="E5">
         <v>6047</v>
@@ -4298,7 +4298,7 @@
         <v>46151.29482400463</v>
       </c>
       <c r="D6" s="1">
-        <v>46151.54479166667</v>
+        <v>46151.29479166667</v>
       </c>
       <c r="E6">
         <v>6339</v>
@@ -4420,7 +4420,7 @@
         <v>46151.29499005787</v>
       </c>
       <c r="D7" s="1">
-        <v>46151.544965277775</v>
+        <v>46151.294965277775</v>
       </c>
       <c r="E7">
         <v>6738</v>
@@ -4563,7 +4563,7 @@
         <v>46151.29516716435</v>
       </c>
       <c r="D8" s="1">
-        <v>46151.54513888889</v>
+        <v>46151.29513888889</v>
       </c>
       <c r="E8">
         <v>7022</v>
@@ -4685,7 +4685,7 @@
         <v>46151.29533501157</v>
       </c>
       <c r="D9" s="1">
-        <v>46151.5453125</v>
+        <v>46151.2953125</v>
       </c>
       <c r="E9">
         <v>7407</v>
@@ -4828,7 +4828,7 @@
         <v>46151.29551344908</v>
       </c>
       <c r="D10" s="1">
-        <v>46151.545486111114</v>
+        <v>46151.295486111114</v>
       </c>
       <c r="E10">
         <v>7678</v>
@@ -4950,7 +4950,7 @@
         <v>46151.29568555555</v>
       </c>
       <c r="D11" s="1">
-        <v>46151.54565972222</v>
+        <v>46151.29565972222</v>
       </c>
       <c r="E11">
         <v>8072</v>
@@ -5093,7 +5093,7 @@
         <v>46151.295866215274</v>
       </c>
       <c r="D12" s="1">
-        <v>46151.54583333333</v>
+        <v>46151.29583333333</v>
       </c>
       <c r="E12">
         <v>8348</v>
@@ -5215,7 +5215,7 @@
         <v>46151.29602851852</v>
       </c>
       <c r="D13" s="1">
-        <v>46151.546006944445</v>
+        <v>46151.296006944445</v>
       </c>
       <c r="E13">
         <v>8733</v>
@@ -5358,7 +5358,7 @@
         <v>46151.29620887731</v>
       </c>
       <c r="D14" s="1">
-        <v>46151.54618055555</v>
+        <v>46151.29618055555</v>
       </c>
       <c r="E14">
         <v>8994</v>
@@ -5480,7 +5480,7 @@
         <v>46151.296376273145</v>
       </c>
       <c r="D15" s="1">
-        <v>46151.54635416667</v>
+        <v>46151.29635416667</v>
       </c>
       <c r="E15">
         <v>9387</v>
@@ -5623,7 +5623,7 @@
         <v>46151.296555775465</v>
       </c>
       <c r="D16" s="1">
-        <v>46151.54652777778</v>
+        <v>46151.29652777778</v>
       </c>
       <c r="E16">
         <v>9683</v>
@@ -5745,7 +5745,7 @@
         <v>46151.29672278935</v>
       </c>
       <c r="D17" s="1">
-        <v>46151.54670138889</v>
+        <v>46151.29670138889</v>
       </c>
       <c r="E17">
         <v>10116</v>
@@ -5888,7 +5888,7 @@
         <v>46151.29690724537</v>
       </c>
       <c r="D18" s="1">
-        <v>46151.546875</v>
+        <v>46151.296875</v>
       </c>
       <c r="E18">
         <v>10408</v>
@@ -6010,7 +6010,7 @@
         <v>46151.29707019676</v>
       </c>
       <c r="D19" s="1">
-        <v>46151.54704861111</v>
+        <v>46151.29704861111</v>
       </c>
       <c r="E19">
         <v>10851</v>
@@ -6153,7 +6153,7 @@
         <v>46151.29725053241</v>
       </c>
       <c r="D20" s="1">
-        <v>46151.54722222222</v>
+        <v>46151.29722222222</v>
       </c>
       <c r="E20">
         <v>11127</v>
@@ -6275,7 +6275,7 @@
         <v>46151.29741792824</v>
       </c>
       <c r="D21" s="1">
-        <v>46151.54739583333</v>
+        <v>46151.29739583333</v>
       </c>
       <c r="E21">
         <v>11560</v>
@@ -6418,7 +6418,7 @@
         <v>46151.29759804398</v>
       </c>
       <c r="D22" s="1">
-        <v>46151.54756944445</v>
+        <v>46151.29756944445</v>
       </c>
       <c r="E22">
         <v>11875</v>
@@ -6540,7 +6540,7 @@
         <v>46151.297764849536</v>
       </c>
       <c r="D23" s="1">
-        <v>46151.547743055555</v>
+        <v>46151.297743055555</v>
       </c>
       <c r="E23">
         <v>12341</v>
@@ -6683,7 +6683,7 @@
         <v>46151.29794866898</v>
       </c>
       <c r="D24" s="1">
-        <v>46151.54791666667</v>
+        <v>46151.29791666667</v>
       </c>
       <c r="E24">
         <v>12636</v>
@@ -6805,7 +6805,7 @@
         <v>46151.298112268516</v>
       </c>
       <c r="D25" s="1">
-        <v>46151.54809027778</v>
+        <v>46151.29809027778</v>
       </c>
       <c r="E25">
         <v>13080</v>
@@ -6948,7 +6948,7 @@
         <v>46151.298291886575</v>
       </c>
       <c r="D26" s="1">
-        <v>46151.548263888886</v>
+        <v>46151.298263888886</v>
       </c>
       <c r="E26">
         <v>13397</v>
@@ -7070,7 +7070,7 @@
         <v>46151.29845960648</v>
       </c>
       <c r="D27" s="1">
-        <v>46151.5484375</v>
+        <v>46151.2984375</v>
       </c>
       <c r="E27">
         <v>13866</v>
@@ -7213,7 +7213,7 @@
         <v>46151.29863881945</v>
       </c>
       <c r="D28" s="1">
-        <v>46151.54861111111</v>
+        <v>46151.29861111111</v>
       </c>
       <c r="E28">
         <v>14185</v>
@@ -7335,7 +7335,7 @@
         <v>46151.298806516206</v>
       </c>
       <c r="D29" s="1">
-        <v>46151.548784722225</v>
+        <v>46151.298784722225</v>
       </c>
       <c r="E29">
         <v>14641</v>
@@ -7478,7 +7478,7 @@
         <v>46151.29899048611</v>
       </c>
       <c r="D30" s="1">
-        <v>46151.54895833333</v>
+        <v>46151.29895833333</v>
       </c>
       <c r="E30">
         <v>14949</v>
@@ -7600,7 +7600,7 @@
         <v>46151.29915414352</v>
       </c>
       <c r="D31" s="1">
-        <v>46151.54913194444</v>
+        <v>46151.29913194444</v>
       </c>
       <c r="E31">
         <v>15394</v>
@@ -7743,7 +7743,7 @@
         <v>46151.29933376158</v>
       </c>
       <c r="D32" s="1">
-        <v>46151.549305555556</v>
+        <v>46151.299305555556</v>
       </c>
       <c r="E32">
         <v>15714</v>
@@ -7865,7 +7865,7 @@
         <v>46151.29950094908</v>
       </c>
       <c r="D33" s="1">
-        <v>46151.549479166664</v>
+        <v>46151.299479166664</v>
       </c>
       <c r="E33">
         <v>16169</v>
@@ -8008,7 +8008,7 @@
         <v>46151.299681157405</v>
       </c>
       <c r="D34" s="1">
-        <v>46151.54965277778</v>
+        <v>46151.29965277778</v>
       </c>
       <c r="E34">
         <v>16469</v>
@@ -8130,7 +8130,7 @@
         <v>46151.29984951389</v>
       </c>
       <c r="D35" s="1">
-        <v>46151.54982638889</v>
+        <v>46151.29982638889</v>
       </c>
       <c r="E35">
         <v>16915</v>
@@ -8273,7 +8273,7 @@
         <v>46151.30003273148</v>
       </c>
       <c r="D36" s="1">
-        <v>46151.55</v>
+        <v>46151.3</v>
       </c>
       <c r="E36">
         <v>17204</v>
@@ -8395,7 +8395,7 @@
         <v>46151.30019628472</v>
       </c>
       <c r="D37" s="1">
-        <v>46151.55017361111</v>
+        <v>46151.30017361111</v>
       </c>
       <c r="E37">
         <v>17634</v>
@@ -8538,7 +8538,7 @@
         <v>46151.300374907405</v>
       </c>
       <c r="D38" s="1">
-        <v>46151.55034722222</v>
+        <v>46151.30034722222</v>
       </c>
       <c r="E38">
         <v>17939</v>
@@ -8660,7 +8660,7 @@
         <v>46151.300541875</v>
       </c>
       <c r="D39" s="1">
-        <v>46151.550520833334</v>
+        <v>46151.300520833334</v>
       </c>
       <c r="E39">
         <v>18396</v>
@@ -8803,7 +8803,7 @@
         <v>46151.30072289352</v>
       </c>
       <c r="D40" s="1">
-        <v>46151.55069444444</v>
+        <v>46151.30069444444</v>
       </c>
       <c r="E40">
         <v>18700</v>
@@ -8925,7 +8925,7 @@
         <v>46151.30089060185</v>
       </c>
       <c r="D41" s="1">
-        <v>46151.55086805556</v>
+        <v>46151.30086805556</v>
       </c>
       <c r="E41">
         <v>19163</v>
@@ -9068,7 +9068,7 @@
         <v>46151.30107415509</v>
       </c>
       <c r="D42" s="1">
-        <v>46151.551041666666</v>
+        <v>46151.301041666666</v>
       </c>
       <c r="E42">
         <v>19468</v>
@@ -9190,7 +9190,7 @@
         <v>46151.30123815972</v>
       </c>
       <c r="D43" s="1">
-        <v>46151.55121527778</v>
+        <v>46151.30121527778</v>
       </c>
       <c r="E43">
         <v>19923</v>
@@ -9333,7 +9333,7 @@
         <v>46151.30141837963</v>
       </c>
       <c r="D44" s="1">
-        <v>46151.55138888889</v>
+        <v>46151.30138888889</v>
       </c>
       <c r="E44">
         <v>20235</v>
@@ -9455,7 +9455,7 @@
         <v>46151.30158386574</v>
       </c>
       <c r="D45" s="1">
-        <v>46151.5515625</v>
+        <v>46151.3015625</v>
       </c>
       <c r="E45">
         <v>20700</v>
@@ -9598,7 +9598,7 @@
         <v>46151.30176504629</v>
       </c>
       <c r="D46" s="1">
-        <v>46151.55173611111</v>
+        <v>46151.30173611111</v>
       </c>
       <c r="E46">
         <v>21013</v>
@@ -9720,7 +9720,7 @@
         <v>46151.30193138889</v>
       </c>
       <c r="D47" s="1">
-        <v>46151.55190972222</v>
+        <v>46151.30190972222</v>
       </c>
       <c r="E47">
         <v>21493</v>
@@ -9863,7 +9863,7 @@
         <v>46151.30211478009</v>
       </c>
       <c r="D48" s="1">
-        <v>46151.552083333336</v>
+        <v>46151.302083333336</v>
       </c>
       <c r="E48">
         <v>21814</v>
@@ -9985,7 +9985,7 @@
         <v>46151.3022784375</v>
       </c>
       <c r="D49" s="1">
-        <v>46151.552256944444</v>
+        <v>46151.302256944444</v>
       </c>
       <c r="E49">
         <v>22288</v>
@@ -10128,7 +10128,7 @@
         <v>46151.30245834491</v>
       </c>
       <c r="D50" s="1">
-        <v>46151.55243055556</v>
+        <v>46151.30243055556</v>
       </c>
       <c r="E50">
         <v>22601</v>
@@ -10250,7 +10250,7 @@
         <v>46151.302625972225</v>
       </c>
       <c r="D51" s="1">
-        <v>46151.55260416667</v>
+        <v>46151.30260416667</v>
       </c>
       <c r="E51">
         <v>23078</v>
@@ -10393,7 +10393,7 @@
         <v>46151.30280596065</v>
       </c>
       <c r="D52" s="1">
-        <v>46151.552777777775</v>
+        <v>46151.302777777775</v>
       </c>
       <c r="E52">
         <v>23395</v>
@@ -10515,7 +10515,7 @@
         <v>46151.30297290509</v>
       </c>
       <c r="D53" s="1">
-        <v>46151.55295138889</v>
+        <v>46151.30295138889</v>
       </c>
       <c r="E53">
         <v>23868</v>
@@ -10658,7 +10658,7 @@
         <v>46151.303157256945</v>
       </c>
       <c r="D54" s="1">
-        <v>46151.553125</v>
+        <v>46151.303125</v>
       </c>
       <c r="E54">
         <v>24176</v>
@@ -10780,7 +10780,7 @@
         <v>46151.30332114583</v>
       </c>
       <c r="D55" s="1">
-        <v>46151.553298611114</v>
+        <v>46151.303298611114</v>
       </c>
       <c r="E55">
         <v>24647</v>
@@ -10923,7 +10923,7 @@
         <v>46151.30350065972</v>
       </c>
       <c r="D56" s="1">
-        <v>46151.55347222222</v>
+        <v>46151.30347222222</v>
       </c>
       <c r="E56">
         <v>24970</v>
@@ -11045,7 +11045,7 @@
         <v>46151.3036677662</v>
       </c>
       <c r="D57" s="1">
-        <v>46151.55364583333</v>
+        <v>46151.30364583333</v>
       </c>
       <c r="E57">
         <v>25440</v>
@@ -11188,7 +11188,7 @@
         <v>46151.30384835648</v>
       </c>
       <c r="D58" s="1">
-        <v>46151.553819444445</v>
+        <v>46151.303819444445</v>
       </c>
       <c r="E58">
         <v>25751</v>
@@ -11310,7 +11310,7 @@
         <v>46151.30401403935</v>
       </c>
       <c r="D59" s="1">
-        <v>46151.55399305555</v>
+        <v>46151.30399305555</v>
       </c>
       <c r="E59">
         <v>26209</v>
@@ -11453,7 +11453,7 @@
         <v>46151.30419883102</v>
       </c>
       <c r="D60" s="1">
-        <v>46151.55416666667</v>
+        <v>46151.30416666667</v>
       </c>
       <c r="E60">
         <v>26532</v>
@@ -11575,7 +11575,7 @@
         <v>46151.304362002316</v>
       </c>
       <c r="D61" s="1">
-        <v>46151.55434027778</v>
+        <v>46151.30434027778</v>
       </c>
       <c r="E61">
         <v>26990</v>
@@ -11718,7 +11718,7 @@
         <v>46151.30454171296</v>
       </c>
       <c r="D62" s="1">
-        <v>46151.55451388889</v>
+        <v>46151.30451388889</v>
       </c>
       <c r="E62">
         <v>27316</v>
@@ -11840,7 +11840,7 @@
         <v>46151.304709351854</v>
       </c>
       <c r="D63" s="1">
-        <v>46151.5546875</v>
+        <v>46151.3046875</v>
       </c>
       <c r="E63">
         <v>27765</v>
@@ -11983,7 +11983,7 @@
         <v>46151.30488856482</v>
       </c>
       <c r="D64" s="1">
-        <v>46151.55486111111</v>
+        <v>46151.30486111111</v>
       </c>
       <c r="E64">
         <v>28061</v>
@@ -12105,7 +12105,7 @@
         <v>46151.305057164354</v>
       </c>
       <c r="D65" s="1">
-        <v>46151.55503472222</v>
+        <v>46151.30503472222</v>
       </c>
       <c r="E65">
         <v>28522</v>
@@ -12248,7 +12248,7 @@
         <v>46151.3052405787</v>
       </c>
       <c r="D66" s="1">
-        <v>46151.55520833333</v>
+        <v>46151.30520833333</v>
       </c>
       <c r="E66">
         <v>28823</v>
@@ -12370,7 +12370,7 @@
         <v>46151.30540423611</v>
       </c>
       <c r="D67" s="1">
-        <v>46151.55538194445</v>
+        <v>46151.30538194445</v>
       </c>
       <c r="E67">
         <v>29281</v>
@@ -12513,7 +12513,7 @@
         <v>46151.30558284722</v>
       </c>
       <c r="D68" s="1">
-        <v>46151.555555555555</v>
+        <v>46151.305555555555</v>
       </c>
       <c r="E68">
         <v>29587</v>
@@ -12635,7 +12635,7 @@
         <v>46151.30583793981</v>
       </c>
       <c r="D69" s="1">
-        <v>46151.55572916667</v>
+        <v>46151.30572916667</v>
       </c>
       <c r="E69">
         <v>30056</v>
@@ -12778,7 +12778,7 @@
         <v>46151.30593079861</v>
       </c>
       <c r="D70" s="1">
-        <v>46151.55590277778</v>
+        <v>46151.30590277778</v>
       </c>
       <c r="E70">
         <v>30375</v>
@@ -12900,7 +12900,7 @@
         <v>46151.306133287035</v>
       </c>
       <c r="D71" s="1">
-        <v>46151.556076388886</v>
+        <v>46151.306076388886</v>
       </c>
       <c r="E71">
         <v>30820</v>
@@ -13043,7 +13043,7 @@
         <v>46151.30628175926</v>
       </c>
       <c r="D72" s="1">
-        <v>46151.55625</v>
+        <v>46151.30625</v>
       </c>
       <c r="E72">
         <v>31113</v>
@@ -13165,7 +13165,7 @@
         <v>46151.30644501157</v>
       </c>
       <c r="D73" s="1">
-        <v>46151.55642361111</v>
+        <v>46151.30642361111</v>
       </c>
       <c r="E73">
         <v>31538</v>
@@ -13308,7 +13308,7 @@
         <v>46151.306625439815</v>
       </c>
       <c r="D74" s="1">
-        <v>46151.556597222225</v>
+        <v>46151.306597222225</v>
       </c>
       <c r="E74">
         <v>31858</v>
@@ -13430,7 +13430,7 @@
         <v>46151.30679219907</v>
       </c>
       <c r="D75" s="1">
-        <v>46151.55677083333</v>
+        <v>46151.30677083333</v>
       </c>
       <c r="E75">
         <v>32296</v>
@@ -13573,7 +13573,7 @@
         <v>46151.30697318287</v>
       </c>
       <c r="D76" s="1">
-        <v>46151.55694444444</v>
+        <v>46151.30694444444</v>
       </c>
       <c r="E76">
         <v>32589</v>
@@ -13695,7 +13695,7 @@
         <v>46151.30713951389</v>
       </c>
       <c r="D77" s="1">
-        <v>46151.557118055556</v>
+        <v>46151.307118055556</v>
       </c>
       <c r="E77">
         <v>33026</v>
@@ -13838,7 +13838,7 @@
         <v>46151.30732443287</v>
       </c>
       <c r="D78" s="1">
-        <v>46151.557291666664</v>
+        <v>46151.307291666664</v>
       </c>
       <c r="E78">
         <v>33328</v>
@@ -13960,7 +13960,7 @@
         <v>46151.307487488426</v>
       </c>
       <c r="D79" s="1">
-        <v>46151.55746527778</v>
+        <v>46151.30746527778</v>
       </c>
       <c r="E79">
         <v>33763</v>
@@ -14103,7 +14103,7 @@
         <v>46151.30766663195</v>
       </c>
       <c r="D80" s="1">
-        <v>46151.55763888889</v>
+        <v>46151.30763888889</v>
       </c>
       <c r="E80">
         <v>34010</v>
@@ -14225,7 +14225,7 @@
         <v>46151.30783421297</v>
       </c>
       <c r="D81" s="1">
-        <v>46151.5578125</v>
+        <v>46151.3078125</v>
       </c>
       <c r="E81">
         <v>34413</v>
@@ -14368,7 +14368,7 @@
         <v>46151.30801364583</v>
       </c>
       <c r="D82" s="1">
-        <v>46151.55798611111</v>
+        <v>46151.30798611111</v>
       </c>
       <c r="E82">
         <v>34614</v>
@@ -14490,7 +14490,7 @@
         <v>46151.3081812963</v>
       </c>
       <c r="D83" s="1">
-        <v>46151.55815972222</v>
+        <v>46151.30815972222</v>
       </c>
       <c r="E83">
         <v>34996</v>
@@ -14633,7 +14633,7 @@
         <v>46151.308364756944</v>
       </c>
       <c r="D84" s="1">
-        <v>46151.558333333334</v>
+        <v>46151.308333333334</v>
       </c>
       <c r="E84">
         <v>35306</v>
@@ -14755,7 +14755,7 @@
         <v>46151.30852957176</v>
       </c>
       <c r="D85" s="1">
-        <v>46151.55850694444</v>
+        <v>46151.30850694444</v>
       </c>
       <c r="E85">
         <v>35753</v>
@@ -14898,7 +14898,7 @@
         <v>46151.30870861111</v>
       </c>
       <c r="D86" s="1">
-        <v>46151.55868055556</v>
+        <v>46151.30868055556</v>
       </c>
       <c r="E86">
         <v>36028</v>
@@ -15020,7 +15020,7 @@
         <v>46151.30887645833</v>
       </c>
       <c r="D87" s="1">
-        <v>46151.558854166666</v>
+        <v>46151.308854166666</v>
       </c>
       <c r="E87">
         <v>36431</v>
@@ -15163,7 +15163,7 @@
         <v>46151.30905582176</v>
       </c>
       <c r="D88" s="1">
-        <v>46151.55902777778</v>
+        <v>46151.30902777778</v>
       </c>
       <c r="E88">
         <v>36648</v>
@@ -15285,7 +15285,7 @@
         <v>46151.30922263889</v>
       </c>
       <c r="D89" s="1">
-        <v>46151.55920138889</v>
+        <v>46151.30920138889</v>
       </c>
       <c r="E89">
         <v>37025</v>
@@ -15428,7 +15428,7 @@
         <v>46151.30940670139</v>
       </c>
       <c r="D90" s="1">
-        <v>46151.559375</v>
+        <v>46151.309375</v>
       </c>
       <c r="E90">
         <v>37206</v>
@@ -15550,7 +15550,7 @@
         <v>46151.30957012731</v>
       </c>
       <c r="D91" s="1">
-        <v>46151.55954861111</v>
+        <v>46151.30954861111</v>
       </c>
       <c r="E91">
         <v>37541</v>
@@ -15693,7 +15693,7 @@
         <v>46151.309750486114</v>
       </c>
       <c r="D92" s="1">
-        <v>46151.55972222222</v>
+        <v>46151.30972222222</v>
       </c>
       <c r="E92">
         <v>37761</v>
@@ -15815,7 +15815,7 @@
         <v>46151.30991833333</v>
       </c>
       <c r="D93" s="1">
-        <v>46151.559895833336</v>
+        <v>46151.309895833336</v>
       </c>
       <c r="E93">
         <v>38230</v>
@@ -15958,7 +15958,7 @@
         <v>46151.310097106485</v>
       </c>
       <c r="D94" s="1">
-        <v>46151.560069444444</v>
+        <v>46151.310069444444</v>
       </c>
       <c r="E94">
         <v>38492</v>
@@ -16080,7 +16080,7 @@
         <v>46151.31026420139</v>
       </c>
       <c r="D95" s="1">
-        <v>46151.56024305556</v>
+        <v>46151.31024305556</v>
       </c>
       <c r="E95">
         <v>38856</v>
@@ -16223,7 +16223,7 @@
         <v>46151.31044877315</v>
       </c>
       <c r="D96" s="1">
-        <v>46151.56041666667</v>
+        <v>46151.31041666667</v>
       </c>
       <c r="E96">
         <v>39080</v>
@@ -16345,7 +16345,7 @@
         <v>46151.31061291667</v>
       </c>
       <c r="D97" s="1">
-        <v>46151.560590277775</v>
+        <v>46151.310590277775</v>
       </c>
       <c r="E97">
         <v>39392</v>
@@ -16488,7 +16488,7 @@
         <v>46151.31079166666</v>
       </c>
       <c r="D98" s="1">
-        <v>46151.56076388889</v>
+        <v>46151.31076388889</v>
       </c>
       <c r="E98">
         <v>39631</v>
@@ -16610,7 +16610,7 @@
         <v>46151.31095895833</v>
       </c>
       <c r="D99" s="1">
-        <v>46151.5609375</v>
+        <v>46151.3109375</v>
       </c>
       <c r="E99">
         <v>40062</v>
@@ -16753,7 +16753,7 @@
         <v>46151.31113962963</v>
       </c>
       <c r="D100" s="1">
-        <v>46151.561111111114</v>
+        <v>46151.311111111114</v>
       </c>
       <c r="E100">
         <v>40212</v>
@@ -16875,7 +16875,7 @@
         <v>46151.31130721065</v>
       </c>
       <c r="D101" s="1">
-        <v>46151.56128472222</v>
+        <v>46151.31128472222</v>
       </c>
       <c r="E101">
         <v>40506</v>
@@ -17018,7 +17018,7 @@
         <v>46151.311490520835</v>
       </c>
       <c r="D102" s="1">
-        <v>46151.56145833333</v>
+        <v>46151.31145833333</v>
       </c>
       <c r="E102">
         <v>40740</v>
@@ -17140,7 +17140,7 @@
         <v>46151.3116571412</v>
       </c>
       <c r="D103" s="1">
-        <v>46151.561631944445</v>
+        <v>46151.311631944445</v>
       </c>
       <c r="E103">
         <v>41128</v>
@@ -17283,7 +17283,7 @@
         <v>46151.311834085645</v>
       </c>
       <c r="D104" s="1">
-        <v>46151.56180555555</v>
+        <v>46151.31180555555</v>
       </c>
       <c r="E104">
         <v>41380</v>
@@ -17405,7 +17405,7 @@
         <v>46151.3120015625</v>
       </c>
       <c r="D105" s="1">
-        <v>46151.56197916667</v>
+        <v>46151.31197916667</v>
       </c>
       <c r="E105">
         <v>41732</v>
@@ -17551,7 +17551,7 @@
         <v>46151.312180706016</v>
       </c>
       <c r="D106" s="1">
-        <v>46151.56215277778</v>
+        <v>46151.31215277778</v>
       </c>
       <c r="E106">
         <v>41836</v>
@@ -17673,7 +17673,7 @@
         <v>46151.31234809028</v>
       </c>
       <c r="D107" s="1">
-        <v>46151.56232638889</v>
+        <v>46151.31232638889</v>
       </c>
       <c r="E107">
         <v>42092</v>
@@ -17816,7 +17816,7 @@
         <v>46151.312531157404</v>
       </c>
       <c r="D108" s="1">
-        <v>46151.5625</v>
+        <v>46151.3125</v>
       </c>
       <c r="E108">
         <v>42194</v>
@@ -17938,7 +17938,7 @@
         <v>46151.31269641204</v>
       </c>
       <c r="D109" s="1">
-        <v>46151.56267361111</v>
+        <v>46151.31267361111</v>
       </c>
       <c r="E109">
         <v>42430</v>
@@ -18081,7 +18081,7 @@
         <v>46151.31287489583</v>
       </c>
       <c r="D110" s="1">
-        <v>46151.56284722222</v>
+        <v>46151.31284722222</v>
       </c>
       <c r="E110">
         <v>42538</v>
@@ -18203,7 +18203,7 @@
         <v>46151.31304636574</v>
       </c>
       <c r="D111" s="1">
-        <v>46151.56302083333</v>
+        <v>46151.31302083333</v>
       </c>
       <c r="E111">
         <v>42762</v>
@@ -18346,7 +18346,7 @@
         <v>46151.31322335648</v>
       </c>
       <c r="D112" s="1">
-        <v>46151.56319444445</v>
+        <v>46151.31319444445</v>
       </c>
       <c r="E112">
         <v>42850</v>
@@ -18468,7 +18468,7 @@
         <v>46151.313390497686</v>
       </c>
       <c r="D113" s="1">
-        <v>46151.563368055555</v>
+        <v>46151.313368055555</v>
       </c>
       <c r="E113">
         <v>43067</v>
@@ -18611,7 +18611,7 @@
         <v>46151.3135740625</v>
       </c>
       <c r="D114" s="1">
-        <v>46151.56354166667</v>
+        <v>46151.31354166667</v>
       </c>
       <c r="E114">
         <v>43162</v>
@@ -18733,7 +18733,7 @@
         <v>46151.31373693287</v>
       </c>
       <c r="D115" s="1">
-        <v>46151.56371527778</v>
+        <v>46151.31371527778</v>
       </c>
       <c r="E115">
         <v>43471</v>
@@ -18876,7 +18876,7 @@
         <v>46151.31391761574</v>
       </c>
       <c r="D116" s="1">
-        <v>46151.563888888886</v>
+        <v>46151.313888888886</v>
       </c>
       <c r="E116">
         <v>43729</v>
@@ -18998,7 +18998,7 @@
         <v>46151.31408494213</v>
       </c>
       <c r="D117" s="1">
-        <v>46151.5640625</v>
+        <v>46151.3140625</v>
       </c>
       <c r="E117">
         <v>44133</v>
@@ -19141,7 +19141,7 @@
         <v>46151.31426475695</v>
       </c>
       <c r="D118" s="1">
-        <v>46151.56423611111</v>
+        <v>46151.31423611111</v>
       </c>
       <c r="E118">
         <v>44389</v>
@@ -19263,7 +19263,7 @@
         <v>46151.31443185185</v>
       </c>
       <c r="D119" s="1">
-        <v>46151.564409722225</v>
+        <v>46151.314409722225</v>
       </c>
       <c r="E119">
         <v>44741</v>
@@ -19406,7 +19406,7 @@
         <v>46151.31461574074</v>
       </c>
       <c r="D120" s="1">
-        <v>46151.56458333333</v>
+        <v>46151.31458333333</v>
       </c>
       <c r="E120">
         <v>44851</v>
@@ -19528,7 +19528,7 @@
         <v>46151.31477871528</v>
       </c>
       <c r="D121" s="1">
-        <v>46151.56475694444</v>
+        <v>46151.31475694444</v>
       </c>
       <c r="E121">
         <v>45092</v>
@@ -19671,7 +19671,7 @@
         <v>46151.3149584375</v>
       </c>
       <c r="D122" s="1">
-        <v>46151.564930555556</v>
+        <v>46151.314930555556</v>
       </c>
       <c r="E122">
         <v>45186</v>
@@ -19793,7 +19793,7 @@
         <v>46151.315125636575</v>
       </c>
       <c r="D123" s="1">
-        <v>46151.565104166664</v>
+        <v>46151.315104166664</v>
       </c>
       <c r="E123">
         <v>45421</v>
@@ -19936,7 +19936,7 @@
         <v>46151.315306666664</v>
       </c>
       <c r="D124" s="1">
-        <v>46151.56527777778</v>
+        <v>46151.31527777778</v>
       </c>
       <c r="E124">
         <v>45527</v>
@@ -20058,7 +20058,7 @@
         <v>46151.31547356481</v>
       </c>
       <c r="D125" s="1">
-        <v>46151.56545138889</v>
+        <v>46151.31545138889</v>
       </c>
       <c r="E125">
         <v>45761</v>
@@ -20201,7 +20201,7 @@
         <v>46151.31565719908</v>
       </c>
       <c r="D126" s="1">
-        <v>46151.565625</v>
+        <v>46151.315625</v>
       </c>
       <c r="E126">
         <v>45885</v>
@@ -20323,7 +20323,7 @@
         <v>46151.315820474534</v>
       </c>
       <c r="D127" s="1">
-        <v>46151.56579861111</v>
+        <v>46151.31579861111</v>
       </c>
       <c r="E127">
         <v>46154</v>
@@ -20466,7 +20466,7 @@
         <v>46151.316000833336</v>
       </c>
       <c r="D128" s="1">
-        <v>46151.56597222222</v>
+        <v>46151.31597222222</v>
       </c>
       <c r="E128">
         <v>46321</v>
@@ -20588,7 +20588,7 @@
         <v>46151.31616710648</v>
       </c>
       <c r="D129" s="1">
-        <v>46151.566145833334</v>
+        <v>46151.316145833334</v>
       </c>
       <c r="E129">
         <v>46602</v>
@@ -20731,7 +20731,7 @@
         <v>46151.31634799769</v>
       </c>
       <c r="D130" s="1">
-        <v>46151.56631944444</v>
+        <v>46151.31631944444</v>
       </c>
       <c r="E130">
         <v>46758</v>
@@ -20853,7 +20853,7 @@
         <v>46151.31651506945</v>
       </c>
       <c r="D131" s="1">
-        <v>46151.56649305556</v>
+        <v>46151.31649305556</v>
       </c>
       <c r="E131">
         <v>47101</v>
@@ -20996,7 +20996,7 @@
         <v>46151.31686234954</v>
       </c>
       <c r="D132" s="1">
-        <v>46151.56684027778</v>
+        <v>46151.31684027778</v>
       </c>
       <c r="E132">
         <v>47598</v>
@@ -21139,7 +21139,7 @@
         <v>46151.31704578704</v>
       </c>
       <c r="D133" s="1">
-        <v>46151.56701388889</v>
+        <v>46151.31701388889</v>
       </c>
       <c r="E133">
         <v>47745</v>
@@ -21261,7 +21261,7 @@
         <v>46151.31720974537</v>
       </c>
       <c r="D134" s="1">
-        <v>46151.5671875</v>
+        <v>46151.3171875</v>
       </c>
       <c r="E134">
         <v>48030</v>
@@ -21404,7 +21404,7 @@
         <v>46151.31739041667</v>
       </c>
       <c r="D135" s="1">
-        <v>46151.56736111111</v>
+        <v>46151.31736111111</v>
       </c>
       <c r="E135">
         <v>48179</v>
@@ -21526,7 +21526,7 @@
         <v>46151.31755734954</v>
       </c>
       <c r="D136" s="1">
-        <v>46151.56753472222</v>
+        <v>46151.31753472222</v>
       </c>
       <c r="E136">
         <v>48468</v>
@@ -21669,7 +21669,7 @@
         <v>46151.31773685185</v>
       </c>
       <c r="D137" s="1">
-        <v>46151.567708333336</v>
+        <v>46151.317708333336</v>
       </c>
       <c r="E137">
         <v>48605</v>
@@ -21791,7 +21791,7 @@
         <v>46151.317904247684</v>
       </c>
       <c r="D138" s="1">
-        <v>46151.567881944444</v>
+        <v>46151.317881944444</v>
       </c>
       <c r="E138">
         <v>48915</v>
@@ -21934,7 +21934,7 @@
         <v>46151.31808736111</v>
       </c>
       <c r="D139" s="1">
-        <v>46151.56805555556</v>
+        <v>46151.31805555556</v>
       </c>
       <c r="E139">
         <v>49065</v>
@@ -22056,7 +22056,7 @@
         <v>46151.318251006946</v>
       </c>
       <c r="D140" s="1">
-        <v>46151.56822916667</v>
+        <v>46151.31822916667</v>
       </c>
       <c r="E140">
         <v>49318</v>
@@ -22199,7 +22199,7 @@
         <v>46151.31843115741</v>
       </c>
       <c r="D141" s="1">
-        <v>46151.568402777775</v>
+        <v>46151.318402777775</v>
       </c>
       <c r="E141">
         <v>49452</v>
@@ -22321,7 +22321,7 @@
         <v>46151.318598564816</v>
       </c>
       <c r="D142" s="1">
-        <v>46151.56857638889</v>
+        <v>46151.31857638889</v>
       </c>
       <c r="E142">
         <v>49697</v>
@@ -22464,7 +22464,7 @@
         <v>46151.318778125</v>
       </c>
       <c r="D143" s="1">
-        <v>46151.56875</v>
+        <v>46151.31875</v>
       </c>
       <c r="E143">
         <v>49852</v>
@@ -22586,7 +22586,7 @@
         <v>46151.31894586806</v>
       </c>
       <c r="D144" s="1">
-        <v>46151.568923611114</v>
+        <v>46151.318923611114</v>
       </c>
       <c r="E144">
         <v>50185</v>
@@ -22729,7 +22729,7 @@
         <v>46151.31913015046</v>
       </c>
       <c r="D145" s="1">
-        <v>46151.56909722222</v>
+        <v>46151.31909722222</v>
       </c>
       <c r="E145">
         <v>50302</v>
@@ -22851,7 +22851,7 @@
         <v>46151.31929266204</v>
       </c>
       <c r="D146" s="1">
-        <v>46151.56927083333</v>
+        <v>46151.31927083333</v>
       </c>
       <c r="E146">
         <v>50567</v>
@@ -22994,7 +22994,7 @@
         <v>46151.319473564814</v>
       </c>
       <c r="D147" s="1">
-        <v>46151.569444444445</v>
+        <v>46151.319444444445</v>
       </c>
       <c r="E147">
         <v>50695</v>
@@ -23116,7 +23116,7 @@
         <v>46151.319640208334</v>
       </c>
       <c r="D148" s="1">
-        <v>46151.56961805555</v>
+        <v>46151.31961805555</v>
       </c>
       <c r="E148">
         <v>50976</v>
@@ -23259,7 +23259,7 @@
         <v>46151.31982</v>
       </c>
       <c r="D149" s="1">
-        <v>46151.56979166667</v>
+        <v>46151.31979166667</v>
       </c>
       <c r="E149">
         <v>51105</v>
@@ -23381,7 +23381,7 @@
         <v>46151.31998665509</v>
       </c>
       <c r="D150" s="1">
-        <v>46151.56996527778</v>
+        <v>46151.31996527778</v>
       </c>
       <c r="E150">
         <v>51365</v>
@@ -23524,7 +23524,7 @@
         <v>46151.32017050926</v>
       </c>
       <c r="D151" s="1">
-        <v>46151.57013888889</v>
+        <v>46151.32013888889</v>
       </c>
       <c r="E151">
         <v>51506</v>
@@ -23646,7 +23646,7 @@
         <v>46151.32033420139</v>
       </c>
       <c r="D152" s="1">
-        <v>46151.5703125</v>
+        <v>46151.3203125</v>
       </c>
       <c r="E152">
         <v>51773</v>
@@ -23789,7 +23789,7 @@
         <v>46151.32051449074</v>
       </c>
       <c r="D153" s="1">
-        <v>46151.57048611111</v>
+        <v>46151.32048611111</v>
       </c>
       <c r="E153">
         <v>51877</v>
@@ -23911,7 +23911,7 @@
         <v>46151.320681840276</v>
       </c>
       <c r="D154" s="1">
-        <v>46151.57065972222</v>
+        <v>46151.32065972222</v>
       </c>
       <c r="E154">
         <v>52113</v>
@@ -24054,7 +24054,7 @@
         <v>46151.32086165509</v>
       </c>
       <c r="D155" s="1">
-        <v>46151.57083333333</v>
+        <v>46151.32083333333</v>
       </c>
       <c r="E155">
         <v>52228</v>
@@ -24176,7 +24176,7 @@
         <v>46151.321027592596</v>
       </c>
       <c r="D156" s="1">
-        <v>46151.57100694445</v>
+        <v>46151.32100694445</v>
       </c>
       <c r="E156">
         <v>52456</v>
@@ -24319,7 +24319,7 @@
         <v>46151.32121271991</v>
       </c>
       <c r="D157" s="1">
-        <v>46151.571180555555</v>
+        <v>46151.321180555555</v>
       </c>
       <c r="E157">
         <v>52582</v>
@@ -24441,7 +24441,7 @@
         <v>46151.321376099535</v>
       </c>
       <c r="D158" s="1">
-        <v>46151.57135416667</v>
+        <v>46151.32135416667</v>
       </c>
       <c r="E158">
         <v>52842</v>
@@ -24584,7 +24584,7 @@
         <v>46151.321556180555</v>
       </c>
       <c r="D159" s="1">
-        <v>46151.57152777778</v>
+        <v>46151.32152777778</v>
       </c>
       <c r="E159">
         <v>52979</v>
@@ -24706,7 +24706,7 @@
         <v>46151.32172399305</v>
       </c>
       <c r="D160" s="1">
-        <v>46151.571701388886</v>
+        <v>46151.321701388886</v>
       </c>
       <c r="E160">
         <v>53244</v>
@@ -24849,7 +24849,7 @@
         <v>46151.32190332176</v>
       </c>
       <c r="D161" s="1">
-        <v>46151.571875</v>
+        <v>46151.321875</v>
       </c>
       <c r="E161">
         <v>53393</v>
@@ -24971,7 +24971,7 @@
         <v>46151.322070104165</v>
       </c>
       <c r="D162" s="1">
-        <v>46151.57204861111</v>
+        <v>46151.32204861111</v>
       </c>
       <c r="E162">
         <v>53664</v>
@@ -25114,7 +25114,7 @@
         <v>46151.32225424769</v>
       </c>
       <c r="D163" s="1">
-        <v>46151.572222222225</v>
+        <v>46151.322222222225</v>
       </c>
       <c r="E163">
         <v>53799</v>
@@ -25236,7 +25236,7 @@
         <v>46151.32241810185</v>
       </c>
       <c r="D164" s="1">
-        <v>46151.57239583333</v>
+        <v>46151.32239583333</v>
       </c>
       <c r="E164">
         <v>54072</v>
@@ -25379,7 +25379,7 @@
         <v>46151.322598321756</v>
       </c>
       <c r="D165" s="1">
-        <v>46151.57256944444</v>
+        <v>46151.32256944444</v>
       </c>
       <c r="E165">
         <v>54206</v>
@@ -25501,7 +25501,7 @@
         <v>46151.322765</v>
       </c>
       <c r="D166" s="1">
-        <v>46151.572743055556</v>
+        <v>46151.322743055556</v>
       </c>
       <c r="E166">
         <v>54470</v>
@@ -25644,7 +25644,7 @@
         <v>46151.32294423611</v>
       </c>
       <c r="D167" s="1">
-        <v>46151.572916666664</v>
+        <v>46151.322916666664</v>
       </c>
       <c r="E167">
         <v>54587</v>
@@ -25766,7 +25766,7 @@
         <v>46151.32311222222</v>
       </c>
       <c r="D168" s="1">
-        <v>46151.57309027778</v>
+        <v>46151.32309027778</v>
       </c>
       <c r="E168">
         <v>54836</v>
@@ -25909,7 +25909,7 @@
         <v>46151.323295462964</v>
       </c>
       <c r="D169" s="1">
-        <v>46151.57326388889</v>
+        <v>46151.32326388889</v>
       </c>
       <c r="E169">
         <v>54945</v>
@@ -26031,7 +26031,7 @@
         <v>46151.32345974537</v>
       </c>
       <c r="D170" s="1">
-        <v>46151.5734375</v>
+        <v>46151.3234375</v>
       </c>
       <c r="E170">
         <v>55198</v>
@@ -26174,7 +26174,7 @@
         <v>46151.32363979167</v>
       </c>
       <c r="D171" s="1">
-        <v>46151.57361111111</v>
+        <v>46151.32361111111</v>
       </c>
       <c r="E171">
         <v>55328</v>
@@ -26296,7 +26296,7 @@
         <v>46151.323806342596</v>
       </c>
       <c r="D172" s="1">
-        <v>46151.57378472222</v>
+        <v>46151.32378472222</v>
       </c>
       <c r="E172">
         <v>55567</v>
@@ -26439,7 +26439,7 @@
         <v>46151.3239865162</v>
       </c>
       <c r="D173" s="1">
-        <v>46151.573958333334</v>
+        <v>46151.323958333334</v>
       </c>
       <c r="E173">
         <v>55703</v>
@@ -26561,7 +26561,7 @@
         <v>46151.324154166665</v>
       </c>
       <c r="D174" s="1">
-        <v>46151.57413194444</v>
+        <v>46151.32413194444</v>
       </c>
       <c r="E174">
         <v>55948</v>
@@ -26704,7 +26704,7 @@
         <v>46151.324337025464</v>
       </c>
       <c r="D175" s="1">
-        <v>46151.57430555556</v>
+        <v>46151.32430555556</v>
       </c>
       <c r="E175">
         <v>56073</v>
@@ -26826,7 +26826,7 @@
         <v>46151.324503055555</v>
       </c>
       <c r="D176" s="1">
-        <v>46151.574479166666</v>
+        <v>46151.324479166666</v>
       </c>
       <c r="E176">
         <v>56321</v>
@@ -26969,7 +26969,7 @@
         <v>46151.32467980324</v>
       </c>
       <c r="D177" s="1">
-        <v>46151.57465277778</v>
+        <v>46151.32465277778</v>
       </c>
       <c r="E177">
         <v>56447</v>
@@ -27091,7 +27091,7 @@
         <v>46151.32484769676</v>
       </c>
       <c r="D178" s="1">
-        <v>46151.57482638889</v>
+        <v>46151.32482638889</v>
       </c>
       <c r="E178">
         <v>56703</v>
@@ -27234,7 +27234,7 @@
         <v>46151.325027175924</v>
       </c>
       <c r="D179" s="1">
-        <v>46151.575</v>
+        <v>46151.325</v>
       </c>
       <c r="E179">
         <v>56835</v>
@@ -27356,7 +27356,7 @@
         <v>46151.32519609954</v>
       </c>
       <c r="D180" s="1">
-        <v>46151.57517361111</v>
+        <v>46151.32517361111</v>
       </c>
       <c r="E180">
         <v>57104</v>
@@ -27499,7 +27499,7 @@
         <v>46151.32537975694</v>
       </c>
       <c r="D181" s="1">
-        <v>46151.57534722222</v>
+        <v>46151.32534722222</v>
       </c>
       <c r="E181">
         <v>57251</v>
@@ -27621,7 +27621,7 @@
         <v>46151.325542743056</v>
       </c>
       <c r="D182" s="1">
-        <v>46151.575520833336</v>
+        <v>46151.325520833336</v>
       </c>
       <c r="E182">
         <v>57516</v>
@@ -27764,7 +27764,7 @@
         <v>46151.32572354167</v>
       </c>
       <c r="D183" s="1">
-        <v>46151.575694444444</v>
+        <v>46151.325694444444</v>
       </c>
       <c r="E183">
         <v>57635</v>
@@ -27886,7 +27886,7 @@
         <v>46151.32588989583</v>
       </c>
       <c r="D184" s="1">
-        <v>46151.57586805556</v>
+        <v>46151.32586805556</v>
       </c>
       <c r="E184">
         <v>57898</v>
@@ -28029,7 +28029,7 @@
         <v>46151.32606922454</v>
       </c>
       <c r="D185" s="1">
-        <v>46151.57604166667</v>
+        <v>46151.32604166667</v>
       </c>
       <c r="E185">
         <v>58035</v>
@@ -28151,7 +28151,7 @@
         <v>46151.326239675924</v>
       </c>
       <c r="D186" s="1">
-        <v>46151.576215277775</v>
+        <v>46151.326215277775</v>
       </c>
       <c r="E186">
         <v>58286</v>
@@ -28294,7 +28294,7 @@
         <v>46151.32642011574</v>
       </c>
       <c r="D187" s="1">
-        <v>46151.57638888889</v>
+        <v>46151.32638888889</v>
       </c>
       <c r="E187">
         <v>58423</v>
@@ -28416,7 +28416,7 @@
         <v>46151.32658320602</v>
       </c>
       <c r="D188" s="1">
-        <v>46151.5765625</v>
+        <v>46151.3265625</v>
       </c>
       <c r="E188">
         <v>58679</v>
@@ -28559,7 +28559,7 @@
         <v>46151.32676369213</v>
       </c>
       <c r="D189" s="1">
-        <v>46151.576736111114</v>
+        <v>46151.326736111114</v>
       </c>
       <c r="E189">
         <v>58826</v>
@@ -28681,7 +28681,7 @@
         <v>46151.32693099537</v>
       </c>
       <c r="D190" s="1">
-        <v>46151.57690972222</v>
+        <v>46151.32690972222</v>
       </c>
       <c r="E190">
         <v>59098</v>
@@ -28824,7 +28824,7 @@
         <v>46151.32711133102</v>
       </c>
       <c r="D191" s="1">
-        <v>46151.57708333333</v>
+        <v>46151.32708333333</v>
       </c>
       <c r="E191">
         <v>59246</v>
@@ -28946,7 +28946,7 @@
         <v>46151.32727912037</v>
       </c>
       <c r="D192" s="1">
-        <v>46151.577256944445</v>
+        <v>46151.327256944445</v>
       </c>
       <c r="E192">
         <v>59573</v>
@@ -29089,7 +29089,7 @@
         <v>46151.3274624537</v>
       </c>
       <c r="D193" s="1">
-        <v>46151.57743055555</v>
+        <v>46151.32743055555</v>
       </c>
       <c r="E193">
         <v>59709</v>
@@ -29211,7 +29211,7 @@
         <v>46151.32762642361</v>
       </c>
       <c r="D194" s="1">
-        <v>46151.57760416667</v>
+        <v>46151.32760416667</v>
       </c>
       <c r="E194">
         <v>59963</v>
@@ -29354,7 +29354,7 @@
         <v>46151.32780594908</v>
       </c>
       <c r="D195" s="1">
-        <v>46151.57777777778</v>
+        <v>46151.32777777778</v>
       </c>
       <c r="E195">
         <v>60083</v>
@@ -29476,7 +29476,7 @@
         <v>46151.327975162036</v>
       </c>
       <c r="D196" s="1">
-        <v>46151.57795138889</v>
+        <v>46151.32795138889</v>
       </c>
       <c r="E196">
         <v>60351</v>
@@ -29619,7 +29619,7 @@
         <v>46151.32815570602</v>
       </c>
       <c r="D197" s="1">
-        <v>46151.578125</v>
+        <v>46151.328125</v>
       </c>
       <c r="E197">
         <v>60516</v>
@@ -29741,7 +29741,7 @@
         <v>46151.32832068287</v>
       </c>
       <c r="D198" s="1">
-        <v>46151.57829861111</v>
+        <v>46151.32829861111</v>
       </c>
       <c r="E198">
         <v>60782</v>
@@ -29884,7 +29884,7 @@
         <v>46151.328504386576</v>
       </c>
       <c r="D199" s="1">
-        <v>46151.57847222222</v>
+        <v>46151.32847222222</v>
       </c>
       <c r="E199">
         <v>60933</v>
@@ -30006,7 +30006,7 @@
         <v>46151.32866799769</v>
       </c>
       <c r="D200" s="1">
-        <v>46151.57864583333</v>
+        <v>46151.32864583333</v>
       </c>
       <c r="E200">
         <v>61198</v>
@@ -30149,7 +30149,7 @@
         <v>46151.328847453704</v>
       </c>
       <c r="D201" s="1">
-        <v>46151.57881944445</v>
+        <v>46151.32881944445</v>
       </c>
       <c r="E201">
         <v>61333</v>
@@ -30271,7 +30271,7 @@
         <v>46151.32901458333</v>
       </c>
       <c r="D202" s="1">
-        <v>46151.578993055555</v>
+        <v>46151.328993055555</v>
       </c>
       <c r="E202">
         <v>61607</v>
@@ -30414,7 +30414,7 @@
         <v>46151.32919521991</v>
       </c>
       <c r="D203" s="1">
-        <v>46151.57916666667</v>
+        <v>46151.32916666667</v>
       </c>
       <c r="E203">
         <v>61770</v>
@@ -30536,7 +30536,7 @@
         <v>46151.32936232639</v>
       </c>
       <c r="D204" s="1">
-        <v>46151.57934027778</v>
+        <v>46151.32934027778</v>
       </c>
       <c r="E204">
         <v>62013</v>
@@ -30679,7 +30679,7 @@
         <v>46151.32954690972</v>
       </c>
       <c r="D205" s="1">
-        <v>46151.579513888886</v>
+        <v>46151.329513888886</v>
       </c>
       <c r="E205">
         <v>62147</v>
@@ -30801,7 +30801,7 @@
         <v>46151.329711886574</v>
       </c>
       <c r="D206" s="1">
-        <v>46151.5796875</v>
+        <v>46151.3296875</v>
       </c>
       <c r="E206">
         <v>62417</v>
@@ -30944,7 +30944,7 @@
         <v>46151.32988909722</v>
       </c>
       <c r="D207" s="1">
-        <v>46151.57986111111</v>
+        <v>46151.32986111111</v>
       </c>
       <c r="E207">
         <v>62570</v>
@@ -31066,7 +31066,7 @@
         <v>46151.33005590278</v>
       </c>
       <c r="D208" s="1">
-        <v>46151.580034722225</v>
+        <v>46151.330034722225</v>
       </c>
       <c r="E208">
         <v>62830</v>
@@ -31209,7 +31209,7 @@
         <v>46151.33023615741</v>
       </c>
       <c r="D209" s="1">
-        <v>46151.58020833333</v>
+        <v>46151.33020833333</v>
       </c>
       <c r="E209">
         <v>62970</v>
@@ -31331,7 +31331,7 @@
         <v>46151.33040571759</v>
       </c>
       <c r="D210" s="1">
-        <v>46151.58038194444</v>
+        <v>46151.33038194444</v>
       </c>
       <c r="E210">
         <v>63229</v>
@@ -31474,7 +31474,7 @@
         <v>46151.33058858796</v>
       </c>
       <c r="D211" s="1">
-        <v>46151.580555555556</v>
+        <v>46151.330555555556</v>
       </c>
       <c r="E211">
         <v>63354</v>
@@ -31596,7 +31596,7 @@
         <v>46151.33075100694</v>
       </c>
       <c r="D212" s="1">
-        <v>46151.580729166664</v>
+        <v>46151.330729166664</v>
       </c>
       <c r="E212">
         <v>63618</v>
@@ -31739,7 +31739,7 @@
         <v>46151.330930729164</v>
       </c>
       <c r="D213" s="1">
-        <v>46151.58090277778</v>
+        <v>46151.33090277778</v>
       </c>
       <c r="E213">
         <v>63748</v>
@@ -31861,7 +31861,7 @@
         <v>46151.33109898148</v>
       </c>
       <c r="D214" s="1">
-        <v>46151.58107638889</v>
+        <v>46151.33107638889</v>
       </c>
       <c r="E214">
         <v>64004</v>
@@ -32004,7 +32004,7 @@
         <v>46151.33127870371</v>
       </c>
       <c r="D215" s="1">
-        <v>46151.58125</v>
+        <v>46151.33125</v>
       </c>
       <c r="E215">
         <v>64165</v>
@@ -32126,7 +32126,7 @@
         <v>46151.33144538195</v>
       </c>
       <c r="D216" s="1">
-        <v>46151.58142361111</v>
+        <v>46151.33142361111</v>
       </c>
       <c r="E216">
         <v>64436</v>
@@ -32269,7 +32269,7 @@
         <v>46151.33162858796</v>
       </c>
       <c r="D217" s="1">
-        <v>46151.58159722222</v>
+        <v>46151.33159722222</v>
       </c>
       <c r="E217">
         <v>64555</v>
@@ -32391,7 +32391,7 @@
         <v>46151.33179256944</v>
       </c>
       <c r="D218" s="1">
-        <v>46151.581770833334</v>
+        <v>46151.331770833334</v>
       </c>
       <c r="E218">
         <v>64818</v>
@@ -32534,7 +32534,7 @@
         <v>46151.331971851854</v>
       </c>
       <c r="D219" s="1">
-        <v>46151.58194444444</v>
+        <v>46151.33194444444</v>
       </c>
       <c r="E219">
         <v>64946</v>
@@ -32656,7 +32656,7 @@
         <v>46151.33214052083</v>
       </c>
       <c r="D220" s="1">
-        <v>46151.58211805556</v>
+        <v>46151.33211805556</v>
       </c>
       <c r="E220">
         <v>65186</v>
@@ -32799,7 +32799,7 @@
         <v>46151.332319837966</v>
       </c>
       <c r="D221" s="1">
-        <v>46151.582291666666</v>
+        <v>46151.332291666666</v>
       </c>
       <c r="E221">
         <v>65326</v>
@@ -32921,7 +32921,7 @@
         <v>46151.332487291664</v>
       </c>
       <c r="D222" s="1">
-        <v>46151.58246527778</v>
+        <v>46151.33246527778</v>
       </c>
       <c r="E222">
         <v>65579</v>
@@ -33064,7 +33064,7 @@
         <v>46151.33267192129</v>
       </c>
       <c r="D223" s="1">
-        <v>46151.58263888889</v>
+        <v>46151.33263888889</v>
       </c>
       <c r="E223">
         <v>65700</v>
@@ -33186,7 +33186,7 @@
         <v>46151.332834050925</v>
       </c>
       <c r="D224" s="1">
-        <v>46151.5828125</v>
+        <v>46151.3328125</v>
       </c>
       <c r="E224">
         <v>65948</v>
@@ -33329,7 +33329,7 @@
         <v>46151.33301451389</v>
       </c>
       <c r="D225" s="1">
-        <v>46151.58298611111</v>
+        <v>46151.33298611111</v>
       </c>
       <c r="E225">
         <v>66084</v>
@@ -33451,7 +33451,7 @@
         <v>46151.33318203704</v>
       </c>
       <c r="D226" s="1">
-        <v>46151.58315972222</v>
+        <v>46151.33315972222</v>
       </c>
       <c r="E226">
         <v>66337</v>
@@ -33594,7 +33594,7 @@
         <v>46151.33336070602</v>
       </c>
       <c r="D227" s="1">
-        <v>46151.583333333336</v>
+        <v>46151.333333333336</v>
       </c>
       <c r="E227">
         <v>66468</v>
@@ -33716,7 +33716,7 @@
         <v>46151.33353081019</v>
       </c>
       <c r="D228" s="1">
-        <v>46151.583506944444</v>
+        <v>46151.333506944444</v>
       </c>
       <c r="E228">
         <v>66712</v>
@@ -33859,7 +33859,7 @@
         <v>46151.33371320602</v>
       </c>
       <c r="D229" s="1">
-        <v>46151.58368055556</v>
+        <v>46151.33368055556</v>
       </c>
       <c r="E229">
         <v>66842</v>
@@ -33981,7 +33981,7 @@
         <v>46151.333875972225</v>
       </c>
       <c r="D230" s="1">
-        <v>46151.58385416667</v>
+        <v>46151.33385416667</v>
       </c>
       <c r="E230">
         <v>67103</v>
@@ -34124,7 +34124,7 @@
         <v>46151.33405517361</v>
       </c>
       <c r="D231" s="1">
-        <v>46151.584027777775</v>
+        <v>46151.334027777775</v>
       </c>
       <c r="E231">
         <v>67230</v>
@@ -34246,7 +34246,7 @@
         <v>46151.33422296296</v>
       </c>
       <c r="D232" s="1">
-        <v>46151.58420138889</v>
+        <v>46151.33420138889</v>
       </c>
       <c r="E232">
         <v>67498</v>
@@ -34389,7 +34389,7 @@
         <v>46151.33440318287</v>
       </c>
       <c r="D233" s="1">
-        <v>46151.584375</v>
+        <v>46151.334375</v>
       </c>
       <c r="E233">
         <v>67620</v>
@@ -34511,7 +34511,7 @@
         <v>46151.33457086806</v>
       </c>
       <c r="D234" s="1">
-        <v>46151.584548611114</v>
+        <v>46151.334548611114</v>
       </c>
       <c r="E234">
         <v>67877</v>
@@ -34654,7 +34654,7 @@
         <v>46151.33475417824</v>
       </c>
       <c r="D235" s="1">
-        <v>46151.58472222222</v>
+        <v>46151.33472222222</v>
       </c>
       <c r="E235">
         <v>67997</v>
@@ -34776,7 +34776,7 @@
         <v>46151.334918217595</v>
       </c>
       <c r="D236" s="1">
-        <v>46151.58489583333</v>
+        <v>46151.33489583333</v>
       </c>
       <c r="E236">
         <v>68257</v>
@@ -34919,7 +34919,7 @@
         <v>46151.33509777778</v>
       </c>
       <c r="D237" s="1">
-        <v>46151.585069444445</v>
+        <v>46151.335069444445</v>
       </c>
       <c r="E237">
         <v>68408</v>
@@ -35041,7 +35041,7 @@
         <v>46151.33526467592</v>
       </c>
       <c r="D238" s="1">
-        <v>46151.58524305555</v>
+        <v>46151.33524305555</v>
       </c>
       <c r="E238">
         <v>68694</v>
@@ -35184,7 +35184,7 @@
         <v>46151.33561170139</v>
       </c>
       <c r="D239" s="1">
-        <v>46151.58559027778</v>
+        <v>46151.33559027778</v>
       </c>
       <c r="E239">
         <v>69077</v>
@@ -35327,7 +35327,7 @@
         <v>46151.3357918287</v>
       </c>
       <c r="D240" s="1">
-        <v>46151.58576388889</v>
+        <v>46151.33576388889</v>
       </c>
       <c r="E240">
         <v>69205</v>
@@ -35449,7 +35449,7 @@
         <v>46151.33595925926</v>
       </c>
       <c r="D241" s="1">
-        <v>46151.5859375</v>
+        <v>46151.3359375</v>
       </c>
       <c r="E241">
         <v>69469</v>
@@ -35592,7 +35592,7 @@
         <v>46151.33614292824</v>
       </c>
       <c r="D242" s="1">
-        <v>46151.58611111111</v>
+        <v>46151.33611111111</v>
       </c>
       <c r="E242">
         <v>69605</v>
@@ -35714,7 +35714,7 @@
         <v>46151.33630623842</v>
       </c>
       <c r="D243" s="1">
-        <v>46151.58628472222</v>
+        <v>46151.33628472222</v>
       </c>
       <c r="E243">
         <v>69851</v>
@@ -35857,7 +35857,7 @@
         <v>46151.33648788194</v>
       </c>
       <c r="D244" s="1">
-        <v>46151.58645833333</v>
+        <v>46151.33645833333</v>
       </c>
       <c r="E244">
         <v>69999</v>
@@ -35979,7 +35979,7 @@
         <v>46151.33665377315</v>
       </c>
       <c r="D245" s="1">
-        <v>46151.58663194445</v>
+        <v>46151.33663194445</v>
       </c>
       <c r="E245">
         <v>70260</v>
@@ -36122,7 +36122,7 @@
         <v>46151.336835277776</v>
       </c>
       <c r="D246" s="1">
-        <v>46151.586805555555</v>
+        <v>46151.336805555555</v>
       </c>
       <c r="E246">
         <v>70389</v>
@@ -36244,7 +36244,7 @@
         <v>46151.33700131944</v>
       </c>
       <c r="D247" s="1">
-        <v>46151.58697916667</v>
+        <v>46151.33697916667</v>
       </c>
       <c r="E247">
         <v>70654</v>
@@ -36387,7 +36387,7 @@
         <v>46151.33718582176</v>
       </c>
       <c r="D248" s="1">
-        <v>46151.58715277778</v>
+        <v>46151.33715277778</v>
       </c>
       <c r="E248">
         <v>70793</v>
@@ -36509,7 +36509,7 @@
         <v>46151.337347719906</v>
       </c>
       <c r="D249" s="1">
-        <v>46151.587326388886</v>
+        <v>46151.337326388886</v>
       </c>
       <c r="E249">
         <v>71044</v>
@@ -36652,7 +36652,7 @@
         <v>46151.337698877316</v>
       </c>
       <c r="D250" s="1">
-        <v>46151.58767361111</v>
+        <v>46151.33767361111</v>
       </c>
       <c r="E250">
         <v>71408</v>
@@ -36795,7 +36795,7 @@
         <v>46151.3378756713</v>
       </c>
       <c r="D251" s="1">
-        <v>46151.587847222225</v>
+        <v>46151.337847222225</v>
       </c>
       <c r="E251">
         <v>71531</v>
@@ -36917,7 +36917,7 @@
         <v>46151.338042152776</v>
       </c>
       <c r="D252" s="1">
-        <v>46151.58802083333</v>
+        <v>46151.33802083333</v>
       </c>
       <c r="E252">
         <v>71787</v>
@@ -37060,7 +37060,7 @@
         <v>46151.33822232639</v>
       </c>
       <c r="D253" s="1">
-        <v>46151.58819444444</v>
+        <v>46151.33819444444</v>
       </c>
       <c r="E253">
         <v>71909</v>
@@ -37182,7 +37182,7 @@
         <v>46151.338389606484</v>
       </c>
       <c r="D254" s="1">
-        <v>46151.588368055556</v>
+        <v>46151.338368055556</v>
       </c>
       <c r="E254">
         <v>72148</v>
@@ -37325,7 +37325,7 @@
         <v>46151.33857353009</v>
       </c>
       <c r="D255" s="1">
-        <v>46151.588541666664</v>
+        <v>46151.338541666664</v>
       </c>
       <c r="E255">
         <v>72270</v>
@@ -37447,7 +37447,7 @@
         <v>46151.33873851852</v>
       </c>
       <c r="D256" s="1">
-        <v>46151.58871527778</v>
+        <v>46151.33871527778</v>
       </c>
       <c r="E256">
         <v>72516</v>
@@ -37590,7 +37590,7 @@
         <v>46151.33891701389</v>
       </c>
       <c r="D257" s="1">
-        <v>46151.58888888889</v>
+        <v>46151.33888888889</v>
       </c>
       <c r="E257">
         <v>72630</v>
@@ -37712,7 +37712,7 @@
         <v>46151.33908467593</v>
       </c>
       <c r="D258" s="1">
-        <v>46151.5890625</v>
+        <v>46151.3390625</v>
       </c>
       <c r="E258">
         <v>72891</v>
@@ -37855,7 +37855,7 @@
         <v>46151.33926385417</v>
       </c>
       <c r="D259" s="1">
-        <v>46151.58923611111</v>
+        <v>46151.33923611111</v>
       </c>
       <c r="E259">
         <v>73037</v>
@@ -37977,7 +37977,7 @@
         <v>46151.33943190972</v>
       </c>
       <c r="D260" s="1">
-        <v>46151.58940972222</v>
+        <v>46151.33940972222</v>
       </c>
       <c r="E260">
         <v>73276</v>
@@ -38120,7 +38120,7 @@
         <v>46151.339615613426</v>
       </c>
       <c r="D261" s="1">
-        <v>46151.589583333334</v>
+        <v>46151.339583333334</v>
       </c>
       <c r="E261">
         <v>73428</v>
@@ -38242,7 +38242,7 @@
         <v>46151.33977899305</v>
       </c>
       <c r="D262" s="1">
-        <v>46151.58975694444</v>
+        <v>46151.33975694444</v>
       </c>
       <c r="E262">
         <v>73708</v>
@@ -38385,7 +38385,7 @@
         <v>46151.3399590625</v>
       </c>
       <c r="D263" s="1">
-        <v>46151.58993055556</v>
+        <v>46151.33993055556</v>
       </c>
       <c r="E263">
         <v>73848</v>
@@ -38507,7 +38507,7 @@
         <v>46151.340125625</v>
       </c>
       <c r="D264" s="1">
-        <v>46151.590104166666</v>
+        <v>46151.340104166666</v>
       </c>
       <c r="E264">
         <v>74110</v>
@@ -38650,7 +38650,7 @@
         <v>46151.34030502315</v>
       </c>
       <c r="D265" s="1">
-        <v>46151.59027777778</v>
+        <v>46151.34027777778</v>
       </c>
       <c r="E265">
         <v>74248</v>
@@ -38772,7 +38772,7 @@
         <v>46151.340473888886</v>
       </c>
       <c r="D266" s="1">
-        <v>46151.59045138889</v>
+        <v>46151.34045138889</v>
       </c>
       <c r="E266">
         <v>74504</v>
@@ -38915,7 +38915,7 @@
         <v>46151.34065675926</v>
       </c>
       <c r="D267" s="1">
-        <v>46151.590625</v>
+        <v>46151.340625</v>
       </c>
       <c r="E267">
         <v>74652</v>
@@ -39037,7 +39037,7 @@
         <v>46151.340820868056</v>
       </c>
       <c r="D268" s="1">
-        <v>46151.59079861111</v>
+        <v>46151.34079861111</v>
       </c>
       <c r="E268">
         <v>74905</v>
@@ -39180,7 +39180,7 @@
         <v>46151.34100017361</v>
       </c>
       <c r="D269" s="1">
-        <v>46151.59097222222</v>
+        <v>46151.34097222222</v>
       </c>
       <c r="E269">
         <v>75055</v>
@@ -39458,7 +39458,7 @@
         <v>46151.341215381944</v>
       </c>
       <c r="D2" s="1">
-        <v>46151.591145833336</v>
+        <v>46151.341145833336</v>
       </c>
       <c r="E2">
         <v>74296</v>
@@ -39565,7 +39565,7 @@
         <v>46151.34134748843</v>
       </c>
       <c r="D3" s="1">
-        <v>46151.591319444444</v>
+        <v>46151.341319444444</v>
       </c>
       <c r="E3">
         <v>73329</v>
@@ -39675,7 +39675,7 @@
         <v>46151.341518217596</v>
       </c>
       <c r="D4" s="1">
-        <v>46151.59149305556</v>
+        <v>46151.34149305556</v>
       </c>
       <c r="E4">
         <v>72363</v>
@@ -39818,7 +39818,7 @@
         <v>46151.34169887732</v>
       </c>
       <c r="D5" s="1">
-        <v>46151.59166666667</v>
+        <v>46151.34166666667</v>
       </c>
       <c r="E5">
         <v>71456</v>
@@ -39940,7 +39940,7 @@
         <v>46151.341862430556</v>
       </c>
       <c r="D6" s="1">
-        <v>46151.591840277775</v>
+        <v>46151.341840277775</v>
       </c>
       <c r="E6">
         <v>70517</v>
@@ -40083,7 +40083,7 @@
         <v>46151.34204181713</v>
       </c>
       <c r="D7" s="1">
-        <v>46151.59201388889</v>
+        <v>46151.34201388889</v>
       </c>
       <c r="E7">
         <v>69638</v>
@@ -40205,7 +40205,7 @@
         <v>46151.34220950231</v>
       </c>
       <c r="D8" s="1">
-        <v>46151.5921875</v>
+        <v>46151.3421875</v>
       </c>
       <c r="E8">
         <v>68789</v>
@@ -40348,7 +40348,7 @@
         <v>46151.342388287034</v>
       </c>
       <c r="D9" s="1">
-        <v>46151.592361111114</v>
+        <v>46151.342361111114</v>
       </c>
       <c r="E9">
         <v>67991</v>
@@ -40470,7 +40470,7 @@
         <v>46151.34256005787</v>
       </c>
       <c r="D10" s="1">
-        <v>46151.59253472222</v>
+        <v>46151.34253472222</v>
       </c>
       <c r="E10">
         <v>67198</v>
@@ -40613,7 +40613,7 @@
         <v>46151.34274013889</v>
       </c>
       <c r="D11" s="1">
-        <v>46151.59270833333</v>
+        <v>46151.34270833333</v>
       </c>
       <c r="E11">
         <v>66311</v>
@@ -40735,7 +40735,7 @@
         <v>46151.342903599536</v>
       </c>
       <c r="D12" s="1">
-        <v>46151.592881944445</v>
+        <v>46151.342881944445</v>
       </c>
       <c r="E12">
         <v>65360</v>
@@ -40878,7 +40878,7 @@
         <v>46151.3430844213</v>
       </c>
       <c r="D13" s="1">
-        <v>46151.59305555555</v>
+        <v>46151.34305555555</v>
       </c>
       <c r="E13">
         <v>64506</v>
@@ -41000,7 +41000,7 @@
         <v>46151.34325138889</v>
       </c>
       <c r="D14" s="1">
-        <v>46151.59322916667</v>
+        <v>46151.34322916667</v>
       </c>
       <c r="E14">
         <v>63646</v>
@@ -41143,7 +41143,7 @@
         <v>46151.34343039352</v>
       </c>
       <c r="D15" s="1">
-        <v>46151.59340277778</v>
+        <v>46151.34340277778</v>
       </c>
       <c r="E15">
         <v>62800</v>
@@ -41265,7 +41265,7 @@
         <v>46151.34359858796</v>
       </c>
       <c r="D16" s="1">
-        <v>46151.59357638889</v>
+        <v>46151.34357638889</v>
       </c>
       <c r="E16">
         <v>62035</v>
@@ -41408,7 +41408,7 @@
         <v>46151.34378150463</v>
       </c>
       <c r="D17" s="1">
-        <v>46151.59375</v>
+        <v>46151.34375</v>
       </c>
       <c r="E17">
         <v>61268</v>
@@ -41530,7 +41530,7 @@
         <v>46151.343945416666</v>
       </c>
       <c r="D18" s="1">
-        <v>46151.59392361111</v>
+        <v>46151.34392361111</v>
       </c>
       <c r="E18">
         <v>60484</v>
@@ -41673,7 +41673,7 @@
         <v>46151.34412634259</v>
       </c>
       <c r="D19" s="1">
-        <v>46151.59409722222</v>
+        <v>46151.34409722222</v>
       </c>
       <c r="E19">
         <v>59735</v>
@@ -41795,7 +41795,7 @@
         <v>46151.34429313657</v>
       </c>
       <c r="D20" s="1">
-        <v>46151.59427083333</v>
+        <v>46151.34427083333</v>
       </c>
       <c r="E20">
         <v>58984</v>
@@ -41938,7 +41938,7 @@
         <v>46151.34447335648</v>
       </c>
       <c r="D21" s="1">
-        <v>46151.59444444445</v>
+        <v>46151.34444444445</v>
       </c>
       <c r="E21">
         <v>58268</v>
@@ -42060,7 +42060,7 @@
         <v>46151.34464015046</v>
       </c>
       <c r="D22" s="1">
-        <v>46151.594618055555</v>
+        <v>46151.344618055555</v>
       </c>
       <c r="E22">
         <v>57562</v>
@@ -42203,7 +42203,7 @@
         <v>46151.34482346065</v>
       </c>
       <c r="D23" s="1">
-        <v>46151.59479166667</v>
+        <v>46151.34479166667</v>
       </c>
       <c r="E23">
         <v>56907</v>
@@ -42325,7 +42325,7 @@
         <v>46151.344986516204</v>
       </c>
       <c r="D24" s="1">
-        <v>46151.59496527778</v>
+        <v>46151.34496527778</v>
       </c>
       <c r="E24">
         <v>56307</v>
@@ -42468,7 +42468,7 @@
         <v>46151.34516684028</v>
       </c>
       <c r="D25" s="1">
-        <v>46151.595138888886</v>
+        <v>46151.345138888886</v>
       </c>
       <c r="E25">
         <v>55699</v>
@@ -42590,7 +42590,7 @@
         <v>46151.34533452546</v>
       </c>
       <c r="D26" s="1">
-        <v>46151.5953125</v>
+        <v>46151.3453125</v>
       </c>
       <c r="E26">
         <v>55111</v>
@@ -42733,7 +42733,7 @@
         <v>46151.34551443287</v>
       </c>
       <c r="D27" s="1">
-        <v>46151.59548611111</v>
+        <v>46151.34548611111</v>
       </c>
       <c r="E27">
         <v>54515</v>
@@ -42855,7 +42855,7 @@
         <v>46151.345685127315</v>
       </c>
       <c r="D28" s="1">
-        <v>46151.595659722225</v>
+        <v>46151.345659722225</v>
       </c>
       <c r="E28">
         <v>53908</v>
@@ -42998,7 +42998,7 @@
         <v>46151.34586543981</v>
       </c>
       <c r="D29" s="1">
-        <v>46151.59583333333</v>
+        <v>46151.34583333333</v>
       </c>
       <c r="E29">
         <v>53337</v>
@@ -43120,7 +43120,7 @@
         <v>46151.34602875</v>
       </c>
       <c r="D30" s="1">
-        <v>46151.59600694444</v>
+        <v>46151.34600694444</v>
       </c>
       <c r="E30">
         <v>52802</v>
@@ -43263,7 +43263,7 @@
         <v>46151.346208703704</v>
       </c>
       <c r="D31" s="1">
-        <v>46151.596180555556</v>
+        <v>46151.346180555556</v>
       </c>
       <c r="E31">
         <v>52234</v>
@@ -43385,7 +43385,7 @@
         <v>46151.34637565972</v>
       </c>
       <c r="D32" s="1">
-        <v>46151.596354166664</v>
+        <v>46151.346354166664</v>
       </c>
       <c r="E32">
         <v>51679</v>
@@ -43528,7 +43528,7 @@
         <v>46151.346555729164</v>
       </c>
       <c r="D33" s="1">
-        <v>46151.59652777778</v>
+        <v>46151.34652777778</v>
       </c>
       <c r="E33">
         <v>51135</v>
@@ -43650,7 +43650,7 @@
         <v>46151.346723125</v>
       </c>
       <c r="D34" s="1">
-        <v>46151.59670138889</v>
+        <v>46151.34670138889</v>
       </c>
       <c r="E34">
         <v>50618</v>
@@ -43793,7 +43793,7 @@
         <v>46151.34690631944</v>
       </c>
       <c r="D35" s="1">
-        <v>46151.596875</v>
+        <v>46151.346875</v>
       </c>
       <c r="E35">
         <v>50082</v>
@@ -43915,7 +43915,7 @@
         <v>46151.347070185184</v>
       </c>
       <c r="D36" s="1">
-        <v>46151.59704861111</v>
+        <v>46151.34704861111</v>
       </c>
       <c r="E36">
         <v>49572</v>
@@ -44058,7 +44058,7 @@
         <v>46151.34725046296</v>
       </c>
       <c r="D37" s="1">
-        <v>46151.59722222222</v>
+        <v>46151.34722222222</v>
       </c>
       <c r="E37">
         <v>49061</v>
@@ -44180,7 +44180,7 @@
         <v>46151.34741780093</v>
       </c>
       <c r="D38" s="1">
-        <v>46151.597395833334</v>
+        <v>46151.347395833334</v>
       </c>
       <c r="E38">
         <v>48571</v>
@@ -44323,7 +44323,7 @@
         <v>46151.34759760417</v>
       </c>
       <c r="D39" s="1">
-        <v>46151.59756944444</v>
+        <v>46151.34756944444</v>
       </c>
       <c r="E39">
         <v>48103</v>
@@ -44445,7 +44445,7 @@
         <v>46151.347764398146</v>
       </c>
       <c r="D40" s="1">
-        <v>46151.59774305556</v>
+        <v>46151.34774305556</v>
       </c>
       <c r="E40">
         <v>47681</v>
@@ -44588,7 +44588,7 @@
         <v>46151.348111597224</v>
       </c>
       <c r="D41" s="1">
-        <v>46151.59809027778</v>
+        <v>46151.34809027778</v>
       </c>
       <c r="E41">
         <v>46837</v>
@@ -44731,7 +44731,7 @@
         <v>46151.34829563658</v>
       </c>
       <c r="D42" s="1">
-        <v>46151.59826388889</v>
+        <v>46151.34826388889</v>
       </c>
       <c r="E42">
         <v>46403</v>
@@ -44853,7 +44853,7 @@
         <v>46151.34846017361</v>
       </c>
       <c r="D43" s="1">
-        <v>46151.5984375</v>
+        <v>46151.3484375</v>
       </c>
       <c r="E43">
         <v>46005</v>
@@ -44996,7 +44996,7 @@
         <v>46151.34863934028</v>
       </c>
       <c r="D44" s="1">
-        <v>46151.59861111111</v>
+        <v>46151.34861111111</v>
       </c>
       <c r="E44">
         <v>45567</v>
@@ -45118,7 +45118,7 @@
         <v>46151.34880545139</v>
       </c>
       <c r="D45" s="1">
-        <v>46151.59878472222</v>
+        <v>46151.34878472222</v>
       </c>
       <c r="E45">
         <v>45134</v>
@@ -45261,7 +45261,7 @@
         <v>46151.34898584491</v>
       </c>
       <c r="D46" s="1">
-        <v>46151.598958333336</v>
+        <v>46151.348958333336</v>
       </c>
       <c r="E46">
         <v>44671</v>
@@ -45383,7 +45383,7 @@
         <v>46151.34915394676</v>
       </c>
       <c r="D47" s="1">
-        <v>46151.599131944444</v>
+        <v>46151.349131944444</v>
       </c>
       <c r="E47">
         <v>44251</v>
@@ -45526,7 +45526,7 @@
         <v>46151.34950148148</v>
       </c>
       <c r="D48" s="1">
-        <v>46151.59947916667</v>
+        <v>46151.34947916667</v>
       </c>
       <c r="E48">
         <v>43374</v>
@@ -45669,7 +45669,7 @@
         <v>46151.34968452546</v>
       </c>
       <c r="D49" s="1">
-        <v>46151.599652777775</v>
+        <v>46151.349652777775</v>
       </c>
       <c r="E49">
         <v>42915</v>
@@ -45791,7 +45791,7 @@
         <v>46151.34984849537</v>
       </c>
       <c r="D50" s="1">
-        <v>46151.59982638889</v>
+        <v>46151.34982638889</v>
       </c>
       <c r="E50">
         <v>42511</v>
@@ -45934,7 +45934,7 @@
         <v>46151.35002849537</v>
       </c>
       <c r="D51" s="1">
-        <v>46151.6</v>
+        <v>46151.35</v>
       </c>
       <c r="E51">
         <v>42062</v>
@@ -46056,7 +46056,7 @@
         <v>46151.35019537037</v>
       </c>
       <c r="D52" s="1">
-        <v>46151.600173611114</v>
+        <v>46151.350173611114</v>
       </c>
       <c r="E52">
         <v>41660</v>
@@ -46199,7 +46199,7 @@
         <v>46151.35037501157</v>
       </c>
       <c r="D53" s="1">
-        <v>46151.60034722222</v>
+        <v>46151.35034722222</v>
       </c>
       <c r="E53">
         <v>41206</v>
@@ -46321,7 +46321,7 @@
         <v>46151.35054335648</v>
       </c>
       <c r="D54" s="1">
-        <v>46151.60052083333</v>
+        <v>46151.35052083333</v>
       </c>
       <c r="E54">
         <v>40811</v>
@@ -46464,7 +46464,7 @@
         <v>46151.35072678241</v>
       </c>
       <c r="D55" s="1">
-        <v>46151.600694444445</v>
+        <v>46151.350694444445</v>
       </c>
       <c r="E55">
         <v>40376</v>
@@ -46586,7 +46586,7 @@
         <v>46151.35088996528</v>
       </c>
       <c r="D56" s="1">
-        <v>46151.60086805555</v>
+        <v>46151.35086805555</v>
       </c>
       <c r="E56">
         <v>40005</v>
@@ -46729,7 +46729,7 @@
         <v>46151.351239247684</v>
       </c>
       <c r="D57" s="1">
-        <v>46151.60121527778</v>
+        <v>46151.35121527778</v>
       </c>
       <c r="E57">
         <v>39223</v>
@@ -46872,7 +46872,7 @@
         <v>46151.3514175</v>
       </c>
       <c r="D58" s="1">
-        <v>46151.60138888889</v>
+        <v>46151.35138888889</v>
       </c>
       <c r="E58">
         <v>38811</v>
@@ -46994,7 +46994,7 @@
         <v>46151.35158634259</v>
       </c>
       <c r="D59" s="1">
-        <v>46151.6015625</v>
+        <v>46151.3515625</v>
       </c>
       <c r="E59">
         <v>38463</v>
@@ -47137,7 +47137,7 @@
         <v>46151.35176480324</v>
       </c>
       <c r="D60" s="1">
-        <v>46151.60173611111</v>
+        <v>46151.35173611111</v>
       </c>
       <c r="E60">
         <v>38069</v>
@@ -47259,7 +47259,7 @@
         <v>46151.351932164354</v>
       </c>
       <c r="D61" s="1">
-        <v>46151.60190972222</v>
+        <v>46151.35190972222</v>
       </c>
       <c r="E61">
         <v>37737</v>
@@ -47402,7 +47402,7 @@
         <v>46151.35227923611</v>
       </c>
       <c r="D62" s="1">
-        <v>46151.60225694445</v>
+        <v>46151.35225694445</v>
       </c>
       <c r="E62">
         <v>37045</v>
@@ -47545,7 +47545,7 @@
         <v>46151.352627465276</v>
       </c>
       <c r="D63" s="1">
-        <v>46151.60260416667</v>
+        <v>46151.35260416667</v>
       </c>
       <c r="E63">
         <v>36362</v>
@@ -47688,7 +47688,7 @@
         <v>46151.35297344907</v>
       </c>
       <c r="D64" s="1">
-        <v>46151.602951388886</v>
+        <v>46151.352951388886</v>
       </c>
       <c r="E64">
         <v>35736</v>
@@ -47831,7 +47831,7 @@
         <v>46151.35331997685</v>
       </c>
       <c r="D65" s="1">
-        <v>46151.60329861111</v>
+        <v>46151.35329861111</v>
       </c>
       <c r="E65">
         <v>35039</v>
@@ -47974,7 +47974,7 @@
         <v>46151.353506527776</v>
       </c>
       <c r="D66" s="1">
-        <v>46151.603472222225</v>
+        <v>46151.353472222225</v>
       </c>
       <c r="E66">
         <v>34653</v>
@@ -48096,7 +48096,7 @@
         <v>46151.35366710648</v>
       </c>
       <c r="D67" s="1">
-        <v>46151.60364583333</v>
+        <v>46151.35364583333</v>
       </c>
       <c r="E67">
         <v>34352</v>
@@ -48239,7 +48239,7 @@
         <v>46151.35384797454</v>
       </c>
       <c r="D68" s="1">
-        <v>46151.60381944444</v>
+        <v>46151.35381944444</v>
       </c>
       <c r="E68">
         <v>33994</v>
@@ -48361,7 +48361,7 @@
         <v>46151.35401559028</v>
       </c>
       <c r="D69" s="1">
-        <v>46151.603993055556</v>
+        <v>46151.353993055556</v>
       </c>
       <c r="E69">
         <v>33684</v>
@@ -48504,7 +48504,7 @@
         <v>46151.35419435185</v>
       </c>
       <c r="D70" s="1">
-        <v>46151.604166666664</v>
+        <v>46151.354166666664</v>
       </c>
       <c r="E70">
         <v>33305</v>
@@ -48626,7 +48626,7 @@
         <v>46151.35436203704</v>
       </c>
       <c r="D71" s="1">
-        <v>46151.60434027778</v>
+        <v>46151.35434027778</v>
       </c>
       <c r="E71">
         <v>32991</v>
@@ -48769,7 +48769,7 @@
         <v>46151.35454597222</v>
       </c>
       <c r="D72" s="1">
-        <v>46151.60451388889</v>
+        <v>46151.35451388889</v>
       </c>
       <c r="E72">
         <v>32639</v>
@@ -48891,7 +48891,7 @@
         <v>46151.35470943287</v>
       </c>
       <c r="D73" s="1">
-        <v>46151.6046875</v>
+        <v>46151.3546875</v>
       </c>
       <c r="E73">
         <v>32331</v>
@@ -49034,7 +49034,7 @@
         <v>46151.354889270835</v>
       </c>
       <c r="D74" s="1">
-        <v>46151.60486111111</v>
+        <v>46151.35486111111</v>
       </c>
       <c r="E74">
         <v>31982</v>
@@ -49156,7 +49156,7 @@
         <v>46151.35505585648</v>
       </c>
       <c r="D75" s="1">
-        <v>46151.60503472222</v>
+        <v>46151.35503472222</v>
       </c>
       <c r="E75">
         <v>31698</v>
@@ -49299,7 +49299,7 @@
         <v>46151.35523608796</v>
       </c>
       <c r="D76" s="1">
-        <v>46151.605208333334</v>
+        <v>46151.355208333334</v>
       </c>
       <c r="E76">
         <v>31369</v>
@@ -49421,7 +49421,7 @@
         <v>46151.35540552084</v>
       </c>
       <c r="D77" s="1">
-        <v>46151.60538194444</v>
+        <v>46151.35538194444</v>
       </c>
       <c r="E77">
         <v>31106</v>
@@ -49564,7 +49564,7 @@
         <v>46151.3555875</v>
       </c>
       <c r="D78" s="1">
-        <v>46151.60555555556</v>
+        <v>46151.35555555556</v>
       </c>
       <c r="E78">
         <v>30765</v>
@@ -49686,7 +49686,7 @@
         <v>46151.35575378472</v>
       </c>
       <c r="D79" s="1">
-        <v>46151.605729166666</v>
+        <v>46151.355729166666</v>
       </c>
       <c r="E79">
         <v>30505</v>
@@ -49829,7 +49829,7 @@
         <v>46151.355930543985</v>
       </c>
       <c r="D80" s="1">
-        <v>46151.60590277778</v>
+        <v>46151.35590277778</v>
       </c>
       <c r="E80">
         <v>30171</v>
@@ -49951,7 +49951,7 @@
         <v>46151.35610094907</v>
       </c>
       <c r="D81" s="1">
-        <v>46151.60607638889</v>
+        <v>46151.35607638889</v>
       </c>
       <c r="E81">
         <v>29929</v>
@@ -50094,7 +50094,7 @@
         <v>46151.356278356485</v>
       </c>
       <c r="D82" s="1">
-        <v>46151.60625</v>
+        <v>46151.35625</v>
       </c>
       <c r="E82">
         <v>29600</v>
@@ -50216,7 +50216,7 @@
         <v>46151.35644931713</v>
       </c>
       <c r="D83" s="1">
-        <v>46151.60642361111</v>
+        <v>46151.35642361111</v>
       </c>
       <c r="E83">
         <v>29359</v>
@@ -50359,7 +50359,7 @@
         <v>46151.35662929398</v>
       </c>
       <c r="D84" s="1">
-        <v>46151.60659722222</v>
+        <v>46151.35659722222</v>
       </c>
       <c r="E84">
         <v>29039</v>
@@ -50481,7 +50481,7 @@
         <v>46151.35679278935</v>
       </c>
       <c r="D85" s="1">
-        <v>46151.606770833336</v>
+        <v>46151.356770833336</v>
       </c>
       <c r="E85">
         <v>28795</v>
@@ -50624,7 +50624,7 @@
         <v>46151.35697231482</v>
       </c>
       <c r="D86" s="1">
-        <v>46151.606944444444</v>
+        <v>46151.356944444444</v>
       </c>
       <c r="E86">
         <v>28478</v>
@@ -50746,7 +50746,7 @@
         <v>46151.35714075231</v>
       </c>
       <c r="D87" s="1">
-        <v>46151.60711805556</v>
+        <v>46151.35711805556</v>
       </c>
       <c r="E87">
         <v>28234</v>
@@ -50889,7 +50889,7 @@
         <v>46151.35731997685</v>
       </c>
       <c r="D88" s="1">
-        <v>46151.60729166667</v>
+        <v>46151.35729166667</v>
       </c>
       <c r="E88">
         <v>27917</v>
@@ -51011,7 +51011,7 @@
         <v>46151.35748748843</v>
       </c>
       <c r="D89" s="1">
-        <v>46151.607465277775</v>
+        <v>46151.357465277775</v>
       </c>
       <c r="E89">
         <v>27663</v>
@@ -51154,7 +51154,7 @@
         <v>46151.357671631944</v>
       </c>
       <c r="D90" s="1">
-        <v>46151.60763888889</v>
+        <v>46151.35763888889</v>
       </c>
       <c r="E90">
         <v>27333</v>
@@ -51276,7 +51276,7 @@
         <v>46151.35783435185</v>
       </c>
       <c r="D91" s="1">
-        <v>46151.6078125</v>
+        <v>46151.3578125</v>
       </c>
       <c r="E91">
         <v>27081</v>
@@ -51419,7 +51419,7 @@
         <v>46151.35801387732</v>
       </c>
       <c r="D92" s="1">
-        <v>46151.607986111114</v>
+        <v>46151.357986111114</v>
       </c>
       <c r="E92">
         <v>26772</v>
@@ -51541,7 +51541,7 @@
         <v>46151.35818195602</v>
       </c>
       <c r="D93" s="1">
-        <v>46151.60815972222</v>
+        <v>46151.35815972222</v>
       </c>
       <c r="E93">
         <v>26530</v>
@@ -51684,7 +51684,7 @@
         <v>46151.35836165509</v>
       </c>
       <c r="D94" s="1">
-        <v>46151.60833333333</v>
+        <v>46151.35833333333</v>
       </c>
       <c r="E94">
         <v>26224</v>
@@ -51806,7 +51806,7 @@
         <v>46151.35852782407</v>
       </c>
       <c r="D95" s="1">
-        <v>46151.608506944445</v>
+        <v>46151.358506944445</v>
       </c>
       <c r="E95">
         <v>25972</v>
@@ -51949,7 +51949,7 @@
         <v>46151.35871261574</v>
       </c>
       <c r="D96" s="1">
-        <v>46151.60868055555</v>
+        <v>46151.35868055555</v>
       </c>
       <c r="E96">
         <v>25636</v>
@@ -52071,7 +52071,7 @@
         <v>46151.35887600695</v>
       </c>
       <c r="D97" s="1">
-        <v>46151.60885416667</v>
+        <v>46151.35885416667</v>
       </c>
       <c r="E97">
         <v>25364</v>
@@ -52214,7 +52214,7 @@
         <v>46151.35905532407</v>
       </c>
       <c r="D98" s="1">
-        <v>46151.60902777778</v>
+        <v>46151.35902777778</v>
       </c>
       <c r="E98">
         <v>25029</v>
@@ -52336,7 +52336,7 @@
         <v>46151.35922417824</v>
       </c>
       <c r="D99" s="1">
-        <v>46151.60920138889</v>
+        <v>46151.35920138889</v>
       </c>
       <c r="E99">
         <v>24761</v>
@@ -52479,7 +52479,7 @@
         <v>46151.35940270833</v>
       </c>
       <c r="D100" s="1">
-        <v>46151.609375</v>
+        <v>46151.359375</v>
       </c>
       <c r="E100">
         <v>24416</v>
@@ -52601,7 +52601,7 @@
         <v>46151.359570266206</v>
       </c>
       <c r="D101" s="1">
-        <v>46151.60954861111</v>
+        <v>46151.35954861111</v>
       </c>
       <c r="E101">
         <v>24138</v>
@@ -52744,7 +52744,7 @@
         <v>46151.35991746528</v>
       </c>
       <c r="D102" s="1">
-        <v>46151.60989583333</v>
+        <v>46151.35989583333</v>
       </c>
       <c r="E102">
         <v>23527</v>
@@ -52887,7 +52887,7 @@
         <v>46151.360100729165</v>
       </c>
       <c r="D103" s="1">
-        <v>46151.61006944445</v>
+        <v>46151.36006944445</v>
       </c>
       <c r="E103">
         <v>23205</v>
@@ -53009,7 +53009,7 @@
         <v>46151.36026616898</v>
       </c>
       <c r="D104" s="1">
-        <v>46151.610243055555</v>
+        <v>46151.360243055555</v>
       </c>
       <c r="E104">
         <v>22947</v>
@@ -53152,7 +53152,7 @@
         <v>46151.360444039354</v>
       </c>
       <c r="D105" s="1">
-        <v>46151.61041666667</v>
+        <v>46151.36041666667</v>
       </c>
       <c r="E105">
         <v>22614</v>
@@ -53274,7 +53274,7 @@
         <v>46151.360654212964</v>
       </c>
       <c r="D106" s="1">
-        <v>46151.61059027778</v>
+        <v>46151.36059027778</v>
       </c>
       <c r="E106">
         <v>22354</v>
@@ -53417,7 +53417,7 @@
         <v>46151.36079412037</v>
       </c>
       <c r="D107" s="1">
-        <v>46151.610763888886</v>
+        <v>46151.360763888886</v>
       </c>
       <c r="E107">
         <v>22027</v>
@@ -53539,7 +53539,7 @@
         <v>46151.36096138889</v>
       </c>
       <c r="D108" s="1">
-        <v>46151.6109375</v>
+        <v>46151.3609375</v>
       </c>
       <c r="E108">
         <v>21765</v>
@@ -53682,7 +53682,7 @@
         <v>46151.36130625</v>
       </c>
       <c r="D109" s="1">
-        <v>46151.611284722225</v>
+        <v>46151.361284722225</v>
       </c>
       <c r="E109">
         <v>21200</v>
@@ -53825,7 +53825,7 @@
         <v>46151.36149141203</v>
       </c>
       <c r="D110" s="1">
-        <v>46151.61145833333</v>
+        <v>46151.36145833333</v>
       </c>
       <c r="E110">
         <v>20892</v>
@@ -53947,7 +53947,7 @@
         <v>46151.36165357639</v>
       </c>
       <c r="D111" s="1">
-        <v>46151.61163194444</v>
+        <v>46151.36163194444</v>
       </c>
       <c r="E111">
         <v>20660</v>
@@ -54090,7 +54090,7 @@
         <v>46151.36183431713</v>
       </c>
       <c r="D112" s="1">
-        <v>46151.611805555556</v>
+        <v>46151.361805555556</v>
       </c>
       <c r="E112">
         <v>20373</v>
@@ -54212,7 +54212,7 @@
         <v>46151.36200114583</v>
       </c>
       <c r="D113" s="1">
-        <v>46151.611979166664</v>
+        <v>46151.361979166664</v>
       </c>
       <c r="E113">
         <v>20151</v>
@@ -54355,7 +54355,7 @@
         <v>46151.36218363426</v>
       </c>
       <c r="D114" s="1">
-        <v>46151.61215277778</v>
+        <v>46151.36215277778</v>
       </c>
       <c r="E114">
         <v>19865</v>
@@ -54477,7 +54477,7 @@
         <v>46151.36234894676</v>
       </c>
       <c r="D115" s="1">
-        <v>46151.61232638889</v>
+        <v>46151.36232638889</v>
       </c>
       <c r="E115">
         <v>19666</v>
@@ -54620,7 +54620,7 @@
         <v>46151.36253224537</v>
       </c>
       <c r="D116" s="1">
-        <v>46151.6125</v>
+        <v>46151.3625</v>
       </c>
       <c r="E116">
         <v>19382</v>
@@ -54742,7 +54742,7 @@
         <v>46151.36269530092</v>
       </c>
       <c r="D117" s="1">
-        <v>46151.61267361111</v>
+        <v>46151.36267361111</v>
       </c>
       <c r="E117">
         <v>19183</v>
@@ -54885,7 +54885,7 @@
         <v>46151.36287575232</v>
       </c>
       <c r="D118" s="1">
-        <v>46151.61284722222</v>
+        <v>46151.36284722222</v>
       </c>
       <c r="E118">
         <v>18884</v>
@@ -55007,7 +55007,7 @@
         <v>46151.36304325231</v>
       </c>
       <c r="D119" s="1">
-        <v>46151.613020833334</v>
+        <v>46151.363020833334</v>
       </c>
       <c r="E119">
         <v>18675</v>
@@ -55150,7 +55150,7 @@
         <v>46151.36322168981</v>
       </c>
       <c r="D120" s="1">
-        <v>46151.61319444444</v>
+        <v>46151.36319444444</v>
       </c>
       <c r="E120">
         <v>18385</v>
@@ -55272,7 +55272,7 @@
         <v>46151.36338918981</v>
       </c>
       <c r="D121" s="1">
-        <v>46151.61336805556</v>
+        <v>46151.36336805556</v>
       </c>
       <c r="E121">
         <v>18165</v>
@@ -55415,7 +55415,7 @@
         <v>46151.36357328704</v>
       </c>
       <c r="D122" s="1">
-        <v>46151.613541666666</v>
+        <v>46151.363541666666</v>
       </c>
       <c r="E122">
         <v>17886</v>
@@ -55537,7 +55537,7 @@
         <v>46151.36373939815</v>
       </c>
       <c r="D123" s="1">
-        <v>46151.61371527778</v>
+        <v>46151.36371527778</v>
       </c>
       <c r="E123">
         <v>17683</v>
@@ -55680,7 +55680,7 @@
         <v>46151.36391714121</v>
       </c>
       <c r="D124" s="1">
-        <v>46151.61388888889</v>
+        <v>46151.36388888889</v>
       </c>
       <c r="E124">
         <v>17404</v>
@@ -55802,7 +55802,7 @@
         <v>46151.36408478009</v>
       </c>
       <c r="D125" s="1">
-        <v>46151.6140625</v>
+        <v>46151.3640625</v>
       </c>
       <c r="E125">
         <v>17196</v>
@@ -55945,7 +55945,7 @@
         <v>46151.36443155092</v>
       </c>
       <c r="D126" s="1">
-        <v>46151.61440972222</v>
+        <v>46151.36440972222</v>
       </c>
       <c r="E126">
         <v>16734</v>
@@ -56088,7 +56088,7 @@
         <v>46151.36461171296</v>
       </c>
       <c r="D127" s="1">
-        <v>46151.614583333336</v>
+        <v>46151.364583333336</v>
       </c>
       <c r="E127">
         <v>16465</v>
@@ -56210,7 +56210,7 @@
         <v>46151.36477915509</v>
       </c>
       <c r="D128" s="1">
-        <v>46151.614756944444</v>
+        <v>46151.364756944444</v>
       </c>
       <c r="E128">
         <v>16272</v>
@@ -56353,7 +56353,7 @@
         <v>46151.36496375</v>
       </c>
       <c r="D129" s="1">
-        <v>46151.61493055556</v>
+        <v>46151.36493055556</v>
       </c>
       <c r="E129">
         <v>15996</v>
@@ -56475,7 +56475,7 @@
         <v>46151.365126805555</v>
       </c>
       <c r="D130" s="1">
-        <v>46151.61510416667</v>
+        <v>46151.36510416667</v>
       </c>
       <c r="E130">
         <v>15804</v>
@@ -56618,7 +56618,7 @@
         <v>46151.36531331018</v>
       </c>
       <c r="D131" s="1">
-        <v>46151.615277777775</v>
+        <v>46151.365277777775</v>
       </c>
       <c r="E131">
         <v>15527</v>
@@ -56740,7 +56740,7 @@
         <v>46151.365481851855</v>
       </c>
       <c r="D132" s="1">
-        <v>46151.61545138889</v>
+        <v>46151.36545138889</v>
       </c>
       <c r="E132">
         <v>15322</v>
@@ -56883,7 +56883,7 @@
         <v>46151.36565267361</v>
       </c>
       <c r="D133" s="1">
-        <v>46151.615625</v>
+        <v>46151.365625</v>
       </c>
       <c r="E133">
         <v>15048</v>
@@ -57005,7 +57005,7 @@
         <v>46151.36582021991</v>
       </c>
       <c r="D134" s="1">
-        <v>46151.615798611114</v>
+        <v>46151.365798611114</v>
       </c>
       <c r="E134">
         <v>14839</v>
@@ -57148,7 +57148,7 @@
         <v>46151.36600459491</v>
       </c>
       <c r="D135" s="1">
-        <v>46151.61597222222</v>
+        <v>46151.36597222222</v>
       </c>
       <c r="E135">
         <v>14549</v>
@@ -57270,7 +57270,7 @@
         <v>46151.36617447917</v>
       </c>
       <c r="D136" s="1">
-        <v>46151.61614583333</v>
+        <v>46151.36614583333</v>
       </c>
       <c r="E136">
         <v>14324</v>
@@ -57413,7 +57413,7 @@
         <v>46151.36634704861</v>
       </c>
       <c r="D137" s="1">
-        <v>46151.616319444445</v>
+        <v>46151.366319444445</v>
       </c>
       <c r="E137">
         <v>14044</v>
@@ -57535,7 +57535,7 @@
         <v>46151.36651392361</v>
       </c>
       <c r="D138" s="1">
-        <v>46151.61649305555</v>
+        <v>46151.36649305555</v>
       </c>
       <c r="E138">
         <v>13821</v>
@@ -57678,7 +57678,7 @@
         <v>46151.36669618056</v>
       </c>
       <c r="D139" s="1">
-        <v>46151.61666666667</v>
+        <v>46151.36666666667</v>
       </c>
       <c r="E139">
         <v>13545</v>
@@ -57800,7 +57800,7 @@
         <v>46151.36686804398</v>
       </c>
       <c r="D140" s="1">
-        <v>46151.61684027778</v>
+        <v>46151.36684027778</v>
       </c>
       <c r="E140">
         <v>13340</v>
@@ -57943,7 +57943,7 @@
         <v>46151.36704719908</v>
       </c>
       <c r="D141" s="1">
-        <v>46151.61701388889</v>
+        <v>46151.36701388889</v>
       </c>
       <c r="E141">
         <v>13059</v>
@@ -58065,7 +58065,7 @@
         <v>46151.36721578704</v>
       </c>
       <c r="D142" s="1">
-        <v>46151.6171875</v>
+        <v>46151.3671875</v>
       </c>
       <c r="E142">
         <v>12867</v>
@@ -58208,7 +58208,7 @@
         <v>46151.367391747684</v>
       </c>
       <c r="D143" s="1">
-        <v>46151.61736111111</v>
+        <v>46151.36736111111</v>
       </c>
       <c r="E143">
         <v>12593</v>
@@ -58330,7 +58330,7 @@
         <v>46151.36756310185</v>
       </c>
       <c r="D144" s="1">
-        <v>46151.61753472222</v>
+        <v>46151.36753472222</v>
       </c>
       <c r="E144">
         <v>12392</v>
@@ -58473,7 +58473,7 @@
         <v>46151.36774252315</v>
       </c>
       <c r="D145" s="1">
-        <v>46151.61770833333</v>
+        <v>46151.36770833333</v>
       </c>
       <c r="E145">
         <v>12108</v>
@@ -58595,7 +58595,7 @@
         <v>46151.36790989583</v>
       </c>
       <c r="D146" s="1">
-        <v>46151.61788194445</v>
+        <v>46151.36788194445</v>
       </c>
       <c r="E146">
         <v>11911</v>
@@ -58738,7 +58738,7 @@
         <v>46151.36808807871</v>
       </c>
       <c r="D147" s="1">
-        <v>46151.618055555555</v>
+        <v>46151.368055555555</v>
       </c>
       <c r="E147">
         <v>11639</v>
@@ -58860,7 +58860,7 @@
         <v>46151.368258877315</v>
       </c>
       <c r="D148" s="1">
-        <v>46151.61822916667</v>
+        <v>46151.36822916667</v>
       </c>
       <c r="E148">
         <v>11445</v>
@@ -59003,7 +59003,7 @@
         <v>46151.368431574076</v>
       </c>
       <c r="D149" s="1">
-        <v>46151.61840277778</v>
+        <v>46151.36840277778</v>
       </c>
       <c r="E149">
         <v>11169</v>
@@ -59125,7 +59125,7 @@
         <v>46151.36860393519</v>
       </c>
       <c r="D150" s="1">
-        <v>46151.618576388886</v>
+        <v>46151.368576388886</v>
       </c>
       <c r="E150">
         <v>10969</v>
@@ -59268,7 +59268,7 @@
         <v>46151.36877869213</v>
       </c>
       <c r="D151" s="1">
-        <v>46151.61875</v>
+        <v>46151.36875</v>
       </c>
       <c r="E151">
         <v>10687</v>
@@ -59390,7 +59390,7 @@
         <v>46151.3689516088</v>
       </c>
       <c r="D152" s="1">
-        <v>46151.61892361111</v>
+        <v>46151.36892361111</v>
       </c>
       <c r="E152">
         <v>10478</v>
@@ -59533,7 +59533,7 @@
         <v>46151.369135416666</v>
       </c>
       <c r="D153" s="1">
-        <v>46151.619097222225</v>
+        <v>46151.369097222225</v>
       </c>
       <c r="E153">
         <v>10195</v>
@@ -59655,7 +59655,7 @@
         <v>46151.369298541664</v>
       </c>
       <c r="D154" s="1">
-        <v>46151.61927083333</v>
+        <v>46151.36927083333</v>
       </c>
       <c r="E154">
         <v>9992</v>
@@ -59798,7 +59798,7 @@
         <v>46151.369477824075</v>
       </c>
       <c r="D155" s="1">
-        <v>46151.61944444444</v>
+        <v>46151.36944444444</v>
       </c>
       <c r="E155">
         <v>9709</v>
@@ -59920,7 +59920,7 @@
         <v>46151.369645983796</v>
       </c>
       <c r="D156" s="1">
-        <v>46151.619618055556</v>
+        <v>46151.369618055556</v>
       </c>
       <c r="E156">
         <v>9499</v>
@@ -60063,7 +60063,7 @@
         <v>46151.36982526621</v>
       </c>
       <c r="D157" s="1">
-        <v>46151.619791666664</v>
+        <v>46151.369791666664</v>
       </c>
       <c r="E157">
         <v>9217</v>
@@ -60185,7 +60185,7 @@
         <v>46151.36999615741</v>
       </c>
       <c r="D158" s="1">
-        <v>46151.61996527778</v>
+        <v>46151.36996527778</v>
       </c>
       <c r="E158">
         <v>9013</v>
@@ -60328,7 +60328,7 @@
         <v>46151.370177372686</v>
       </c>
       <c r="D159" s="1">
-        <v>46151.62013888889</v>
+        <v>46151.37013888889</v>
       </c>
       <c r="E159">
         <v>8741</v>
@@ -60450,7 +60450,7 @@
         <v>46151.37034071759</v>
       </c>
       <c r="D160" s="1">
-        <v>46151.6203125</v>
+        <v>46151.3703125</v>
       </c>
       <c r="E160">
         <v>8547</v>
@@ -60593,7 +60593,7 @@
         <v>46151.37052019676</v>
       </c>
       <c r="D161" s="1">
-        <v>46151.62048611111</v>
+        <v>46151.37048611111</v>
       </c>
       <c r="E161">
         <v>8295</v>
@@ -60715,7 +60715,7 @@
         <v>46151.37068774305</v>
       </c>
       <c r="D162" s="1">
-        <v>46151.62065972222</v>
+        <v>46151.37065972222</v>
       </c>
       <c r="E162">
         <v>8120</v>
@@ -60858,7 +60858,7 @@
         <v>46151.37086673611</v>
       </c>
       <c r="D163" s="1">
-        <v>46151.620833333334</v>
+        <v>46151.370833333334</v>
       </c>
       <c r="E163">
         <v>7862</v>
@@ -60980,7 +60980,7 @@
         <v>46151.37103400463</v>
       </c>
       <c r="D164" s="1">
-        <v>46151.62100694444</v>
+        <v>46151.37100694444</v>
       </c>
       <c r="E164">
         <v>7684</v>
@@ -61123,7 +61123,7 @@
         <v>46151.37122221065</v>
       </c>
       <c r="D165" s="1">
-        <v>46151.62118055556</v>
+        <v>46151.37118055556</v>
       </c>
       <c r="E165">
         <v>7442</v>
@@ -61245,7 +61245,7 @@
         <v>46151.37138224537</v>
       </c>
       <c r="D166" s="1">
-        <v>46151.621354166666</v>
+        <v>46151.371354166666</v>
       </c>
       <c r="E166">
         <v>7276</v>
@@ -61388,7 +61388,7 @@
         <v>46151.37156221065</v>
       </c>
       <c r="D167" s="1">
-        <v>46151.62152777778</v>
+        <v>46151.37152777778</v>
       </c>
       <c r="E167">
         <v>7022</v>
@@ -61510,7 +61510,7 @@
         <v>46151.371728715276</v>
       </c>
       <c r="D168" s="1">
-        <v>46151.62170138889</v>
+        <v>46151.37170138889</v>
       </c>
       <c r="E168">
         <v>6857</v>
@@ -61653,7 +61653,7 @@
         <v>46151.37191054398</v>
       </c>
       <c r="D169" s="1">
-        <v>46151.621875</v>
+        <v>46151.371875</v>
       </c>
       <c r="E169">
         <v>6628</v>
@@ -61775,7 +61775,7 @@
         <v>46151.37207716435</v>
       </c>
       <c r="D170" s="1">
-        <v>46151.62204861111</v>
+        <v>46151.37204861111</v>
       </c>
       <c r="E170">
         <v>6452</v>
@@ -61918,7 +61918,7 @@
         <v>46151.37226084491</v>
       </c>
       <c r="D171" s="1">
-        <v>46151.62222222222</v>
+        <v>46151.37222222222</v>
       </c>
       <c r="E171">
         <v>6205</v>
@@ -62040,7 +62040,7 @@
         <v>46151.3724237037</v>
       </c>
       <c r="D172" s="1">
-        <v>46151.622395833336</v>
+        <v>46151.372395833336</v>
       </c>
       <c r="E172">
         <v>6038</v>
@@ -62183,7 +62183,7 @@
         <v>46151.3726071875</v>
       </c>
       <c r="D173" s="1">
-        <v>46151.622569444444</v>
+        <v>46151.372569444444</v>
       </c>
       <c r="E173">
         <v>5811</v>
@@ -62305,7 +62305,7 @@
         <v>46151.372770925926</v>
       </c>
       <c r="D174" s="1">
-        <v>46151.62274305556</v>
+        <v>46151.37274305556</v>
       </c>
       <c r="E174">
         <v>5670</v>
@@ -62448,7 +62448,7 @@
         <v>46151.3729509375</v>
       </c>
       <c r="D175" s="1">
-        <v>46151.62291666667</v>
+        <v>46151.37291666667</v>
       </c>
       <c r="E175">
         <v>5460</v>
@@ -62570,7 +62570,7 @@
         <v>46151.37311871528</v>
       </c>
       <c r="D176" s="1">
-        <v>46151.623090277775</v>
+        <v>46151.373090277775</v>
       </c>
       <c r="E176">
         <v>5313</v>
@@ -62713,7 +62713,7 @@
         <v>46151.37330482639</v>
       </c>
       <c r="D177" s="1">
-        <v>46151.62326388889</v>
+        <v>46151.37326388889</v>
       </c>
       <c r="E177">
         <v>5106</v>
@@ -62835,7 +62835,7 @@
         <v>46151.37346509259</v>
       </c>
       <c r="D178" s="1">
-        <v>46151.6234375</v>
+        <v>46151.3734375</v>
       </c>
       <c r="E178">
         <v>4946</v>
@@ -62978,7 +62978,7 @@
         <v>46151.37364788194</v>
       </c>
       <c r="D179" s="1">
-        <v>46151.623611111114</v>
+        <v>46151.373611111114</v>
       </c>
       <c r="E179">
         <v>4722</v>
@@ -63100,7 +63100,7 @@
         <v>46151.37399335648</v>
       </c>
       <c r="D180" s="1">
-        <v>46151.62395833333</v>
+        <v>46151.37395833333</v>
       </c>
       <c r="E180">
         <v>4692</v>
